--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7173D99A-F1A7-4932-9432-26E019E01B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F453817-8A40-45D9-A56D-61C9B77B1305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="25">
   <si>
     <t>Booking</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabaar </t>
   </si>
 </sst>
 </file>
@@ -218,7 +221,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,6 +243,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -500,6 +509,9 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -878,103 +890,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="46" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -991,16 +1003,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1008,16 +1020,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1130,29 +1142,39 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="11">
+        <v>40</v>
+      </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>80</v>
+      </c>
+      <c r="U8" s="11">
+        <v>40</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>2</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>9.9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>9.9</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -1272,29 +1294,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>80</v>
+      </c>
+      <c r="P10" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>20</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>124</v>
+      </c>
+      <c r="T10" s="11">
+        <v>124</v>
+      </c>
+      <c r="U10" s="11">
+        <v>92</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>15.8</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>15.8</v>
+        <v>3.8000000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -1467,15 +1505,15 @@
       <c r="N14" s="7"/>
       <c r="O14" s="24">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="P14" s="24">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="24">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="R14" s="24">
         <f t="shared" si="6"/>
@@ -1483,19 +1521,19 @@
       </c>
       <c r="S14" s="24">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>228</v>
       </c>
       <c r="T14" s="24">
         <f t="shared" si="6"/>
-        <v>53</v>
+        <v>257</v>
       </c>
       <c r="U14" s="24">
         <f t="shared" si="6"/>
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="V14" s="19">
         <f>SUM(O14:U14)</f>
-        <v>359</v>
+        <v>1039</v>
       </c>
       <c r="W14" s="29"/>
       <c r="Y14" s="34">
@@ -1504,11 +1542,11 @@
       </c>
       <c r="Z14" s="35">
         <f>SUM(Z8:Z13)</f>
-        <v>8.9749999999999996</v>
+        <v>25.975000000000001</v>
       </c>
       <c r="AA14" s="45">
         <f>SUM(AA8:AA13)</f>
-        <v>26.775000000000002</v>
+        <v>9.7750000000000021</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1555,15 +1593,15 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0.875</v>
+        <v>1.875</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
@@ -1571,19 +1609,19 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>1.325</v>
+        <v>6.4249999999999998</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>1.375</v>
+        <v>4.6749999999999998</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>8.9749999999999996</v>
+        <v>25.975000000000001</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -1592,11 +1630,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0.22437499999999999</v>
+        <v>0.64937500000000004</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0.66937500000000005</v>
+        <v>0.24437500000000006</v>
       </c>
     </row>
   </sheetData>
@@ -1663,103 +1701,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1776,16 +1814,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1793,16 +1831,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2384,103 +2422,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2497,16 +2535,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2514,16 +2552,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3105,103 +3143,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3218,16 +3256,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3235,16 +3273,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3826,103 +3864,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3939,16 +3977,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3956,16 +3994,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4547,103 +4585,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4660,16 +4698,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4677,16 +4715,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5268,103 +5306,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5381,16 +5419,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5398,16 +5436,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5989,103 +6027,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6102,16 +6140,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6119,16 +6157,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6710,103 +6748,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6823,16 +6861,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6840,16 +6878,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7431,103 +7469,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7544,16 +7582,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7561,16 +7599,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8152,103 +8190,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8265,16 +8303,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8282,16 +8320,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8873,103 +8911,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8986,16 +9024,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9003,16 +9041,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9092,13 +9130,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -9139,30 +9177,16 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
-        <v>135</v>
-      </c>
-      <c r="D9" s="11">
-        <v>64</v>
-      </c>
-      <c r="E9" s="11">
-        <v>40</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>108</v>
-      </c>
-      <c r="H9" s="11">
-        <v>87</v>
-      </c>
-      <c r="I9" s="11">
-        <v>105</v>
-      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>13.475</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12">
         <v>8</v>
@@ -9186,7 +9210,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>13.475</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -9194,7 +9218,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>13.475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9202,28 +9226,16 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11">
-        <v>150</v>
-      </c>
-      <c r="D10" s="11">
-        <v>70</v>
-      </c>
-      <c r="E10" s="11">
-        <v>90</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11">
-        <v>120</v>
-      </c>
-      <c r="H10" s="11">
-        <v>150</v>
-      </c>
-      <c r="I10" s="11">
-        <v>100</v>
-      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K10" s="12">
         <v>10</v>
@@ -9247,7 +9259,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -9255,7 +9267,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9263,13 +9275,13 @@
       <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9310,13 +9322,13 @@
       <c r="B12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9393,15 +9405,15 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
@@ -9409,19 +9421,19 @@
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>1219</v>
+        <v>0</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -9461,7 +9473,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>30.475000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -9469,7 +9481,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>30.475000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9479,15 +9491,15 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>7.125</v>
+        <v>0</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
@@ -9495,19 +9507,19 @@
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>5.9249999999999998</v>
+        <v>0</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>5.125</v>
+        <v>0</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>30.475000000000001</v>
+        <v>0</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -9549,7 +9561,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0.76187500000000008</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -9557,7 +9569,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0.76187500000000008</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9624,103 +9636,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9737,16 +9749,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9754,16 +9766,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -10345,103 +10357,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10458,16 +10470,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10475,16 +10487,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11066,103 +11078,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11179,16 +11191,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11196,16 +11208,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11787,103 +11799,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11900,16 +11912,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11917,16 +11929,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12508,103 +12520,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12621,16 +12633,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12638,16 +12650,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13229,103 +13241,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13342,16 +13354,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13359,16 +13371,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13950,103 +13962,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14063,16 +14075,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14080,16 +14092,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14671,103 +14683,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14784,16 +14796,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14801,16 +14813,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15392,103 +15404,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15505,16 +15517,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15522,16 +15534,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16113,103 +16125,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16226,16 +16238,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16243,16 +16255,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16834,103 +16846,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16947,16 +16959,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16964,16 +16976,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17053,16 +17065,28 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="C8" s="11">
+        <v>150</v>
+      </c>
+      <c r="D8" s="11">
+        <v>70</v>
+      </c>
+      <c r="E8" s="11">
+        <v>90</v>
+      </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="G8" s="11">
+        <v>120</v>
+      </c>
+      <c r="H8" s="11">
+        <v>150</v>
+      </c>
+      <c r="I8" s="11">
+        <v>100</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="13"/>
@@ -17070,29 +17094,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>120</v>
+      </c>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>73</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>110</v>
+      </c>
+      <c r="T8" s="11">
+        <v>110</v>
+      </c>
+      <c r="U8" s="11">
+        <v>160</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>16.324999999999999</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>16.324999999999999</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>0.67500000000000071</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17100,16 +17140,30 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>135</v>
+      </c>
+      <c r="D9" s="11">
+        <v>64</v>
+      </c>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>108</v>
+      </c>
+      <c r="H9" s="11">
+        <v>87</v>
+      </c>
+      <c r="I9" s="11">
+        <v>105</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
+        <v>13.475</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
@@ -17117,29 +17171,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>135</v>
+      </c>
+      <c r="P9" s="11">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>80</v>
+      </c>
+      <c r="T9" s="11">
+        <v>65</v>
+      </c>
+      <c r="U9" s="11">
+        <v>75</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>11.475</v>
+      </c>
+      <c r="W9" s="12">
+        <v>5</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>13.475</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>11.475</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -17324,15 +17394,15 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
@@ -17340,34 +17410,34 @@
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>1219</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
@@ -17375,32 +17445,32 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>30.475000000000001</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>27.799999999999997</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>2.6750000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17410,15 +17480,15 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>7.125</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
@@ -17426,19 +17496,19 @@
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.9249999999999998</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.125</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>30.475000000000001</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -17447,15 +17517,15 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.8250000000000002</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
@@ -17463,32 +17533,32 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.375</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>0.76187500000000008</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>6.6875000000000018E-2</v>
       </c>
     </row>
   </sheetData>
@@ -17555,103 +17625,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17668,16 +17738,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17685,16 +17755,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18240,16 +18310,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="50" t="s">
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -18618,103 +18688,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18731,16 +18801,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18748,16 +18818,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18837,18 +18907,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>212</v>
+      </c>
+      <c r="D8" s="11">
+        <v>92</v>
+      </c>
+      <c r="E8" s="11">
+        <v>102</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>195</v>
+      </c>
+      <c r="H8" s="11">
+        <v>160</v>
+      </c>
+      <c r="I8" s="11">
+        <v>195</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>23.9</v>
+      </c>
+      <c r="K8" s="12">
+        <v>21</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -18868,7 +18954,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -18876,13 +18962,13 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -18892,10 +18978,11 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>8</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -18909,21 +18996,21 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V12" si="0">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
-        <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y13" si="1">J9</f>
+        <v>6</v>
       </c>
       <c r="Z9" s="40">
-        <f t="shared" ref="Z9:Z13" si="3">V9</f>
+        <f t="shared" ref="Z9:Z13" si="2">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="41">
-        <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <f t="shared" ref="AA9:AA13" si="3">Y9-Z9</f>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -18931,18 +19018,32 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="C10" s="11">
+        <v>80</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11">
+        <v>100</v>
+      </c>
+      <c r="H10" s="11">
+        <v>60</v>
+      </c>
+      <c r="I10" s="11">
+        <v>120</v>
+      </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <f t="shared" ref="J9:J12" si="4">SUM(C10:I10)/40</f>
+        <v>9</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -18956,21 +19057,21 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Z10" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="40">
+      <c r="AA10" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="41">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -18979,15 +19080,27 @@
         <v>17</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>200</v>
+      </c>
+      <c r="E11" s="11">
+        <v>240</v>
+      </c>
+      <c r="F11" s="11">
+        <v>240</v>
+      </c>
+      <c r="G11" s="11">
+        <v>320</v>
+      </c>
+      <c r="H11" s="11">
+        <v>320</v>
+      </c>
+      <c r="I11" s="11">
+        <v>600</v>
+      </c>
       <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="13"/>
@@ -19003,21 +19116,21 @@
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="Z11" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="40">
+      <c r="AA11" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="41">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -19033,7 +19146,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K12" s="12"/>
@@ -19050,20 +19163,20 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="40">
+      <c r="AA12" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="41">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -19091,15 +19204,15 @@
       <c r="V13" s="15"/>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="40">
+      <c r="AA13" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="41">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -19108,35 +19221,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>3236</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -19176,7 +19289,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>86.9</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -19184,7 +19297,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>86.9</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19194,35 +19307,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.375</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.875</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -19264,7 +19377,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>2.1725000000000003</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -19272,7 +19385,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>2.1725000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -19339,103 +19452,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19452,16 +19565,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19469,16 +19582,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20060,103 +20173,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20173,16 +20286,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20190,16 +20303,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20781,103 +20894,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20894,16 +21007,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20911,16 +21024,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21502,103 +21615,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21615,16 +21728,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21632,16 +21745,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22223,103 +22336,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="Y3" s="50" t="s">
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="Y3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22336,16 +22449,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22353,16 +22466,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49" t="s">
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F453817-8A40-45D9-A56D-61C9B77B1305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218F41BE-2971-4B0B-A3AA-B6866C5B0A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -129,14 +129,14 @@
     <t>Return</t>
   </si>
   <si>
-    <t xml:space="preserve">Jabaar </t>
+    <t>Jabbar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,6 +215,43 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -409,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -528,6 +565,66 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2059,7 +2156,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -2076,7 +2173,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2106,7 +2203,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -2123,7 +2220,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -2780,7 +2877,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -2797,7 +2894,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2827,7 +2924,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -2844,7 +2941,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -3501,7 +3598,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -3518,7 +3615,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -3548,7 +3645,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -3565,7 +3662,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -4222,7 +4319,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -4239,7 +4336,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -4269,7 +4366,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -4286,7 +4383,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -4943,7 +5040,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -4960,7 +5057,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -4990,7 +5087,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -5007,7 +5104,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -5664,7 +5761,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -5681,7 +5778,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -5711,7 +5808,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -5728,7 +5825,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -6385,7 +6482,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -6402,7 +6499,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -6432,7 +6529,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -6449,7 +6546,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -7106,7 +7203,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -7123,7 +7220,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7153,7 +7250,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -7170,7 +7267,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -7827,7 +7924,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -7844,7 +7941,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7874,7 +7971,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -7891,7 +7988,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -8548,7 +8645,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -8565,7 +8662,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -8595,7 +8692,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -8612,7 +8709,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -17088,7 +17185,9 @@
         <f>SUM(C8:I8)/40</f>
         <v>17</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="12">
+        <v>17</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -17165,7 +17264,9 @@
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>13.475</v>
       </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="12">
+        <v>7</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -18940,35 +19041,51 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>212</v>
+      </c>
+      <c r="P8" s="11">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>92</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>180</v>
+      </c>
+      <c r="T8" s="11">
+        <v>150</v>
+      </c>
+      <c r="U8" s="11">
+        <v>180</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>22.65</v>
+      </c>
+      <c r="W8" s="12">
+        <v>23</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>23.9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>23.9</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -18978,11 +19095,10 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <v>6</v>
-      </c>
-      <c r="K9" s="12">
-        <v>8</v>
-      </c>
+        <f>SUM(C9:I9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -19002,7 +19118,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="1">J9</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="2">V9</f>
@@ -19010,7 +19126,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="3">Y9-Z9</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -19038,7 +19154,7 @@
         <v>120</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" ref="J9:J12" si="4">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J12" si="4">SUM(C10:I10)/40</f>
         <v>9</v>
       </c>
       <c r="K10" s="12">
@@ -19049,29 +19165,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>80</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>60</v>
+      </c>
+      <c r="T10" s="11">
+        <v>20</v>
+      </c>
+      <c r="U10" s="11">
+        <v>40</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -19102,7 +19234,9 @@
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>1</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -19136,24 +19270,40 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C12" s="11">
+        <v>37</v>
+      </c>
+      <c r="D12" s="11">
+        <v>50</v>
+      </c>
+      <c r="E12" s="11">
+        <v>51</v>
+      </c>
+      <c r="F12" s="11">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11">
+        <v>33</v>
+      </c>
+      <c r="H12" s="11">
+        <v>26</v>
+      </c>
+      <c r="I12" s="11">
+        <v>36</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>8</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -19169,7 +19319,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="2"/>
@@ -19177,7 +19327,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -19221,50 +19371,50 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>615</v>
+        <v>648</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>915</v>
+        <v>951</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>3236</v>
+        <v>3496</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
@@ -19272,32 +19422,32 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>86.9</v>
+        <v>87.4</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>27.65</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>86.9</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19307,35 +19457,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>7.3</v>
+        <v>8.2249999999999996</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>7.3</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>8.5500000000000007</v>
+        <v>9.8249999999999993</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>15.375</v>
+        <v>16.2</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>13.5</v>
+        <v>14.15</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>22.875</v>
+        <v>23.774999999999999</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>80.900000000000006</v>
+        <v>87.4</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -19344,15 +19494,15 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
@@ -19360,32 +19510,32 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>27.65</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>2.1725000000000003</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.69124999999999992</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>2.1725000000000003</v>
+        <v>1.4937499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -19404,18 +19554,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3A0396-7890-4995-B70F-491025A8A037}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
     <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
@@ -19431,15 +19580,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -19451,18 +19603,20 @@
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
       <c r="M2" s="1"/>
       <c r="N2" s="48" t="s">
         <v>1</v>
@@ -19477,16 +19631,18 @@
       <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
       <c r="M3" s="1"/>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -19504,16 +19660,18 @@
       <c r="AA3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
       <c r="M4" s="1"/>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
@@ -19529,16 +19687,18 @@
       <c r="AA4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
       <c r="M5" s="1"/>
       <c r="N5" s="49"/>
       <c r="O5" s="49"/>
@@ -19560,23 +19720,24 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="52"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="5"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="52"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
@@ -19599,38 +19760,38 @@
       <c r="AA6" s="18"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="60"/>
+      <c r="B7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="13"/>
+      <c r="L7" s="67"/>
       <c r="M7" s="6"/>
       <c r="N7" s="7" t="s">
         <v>5</v>
@@ -19667,23 +19828,39 @@
       <c r="AA7" s="18"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="15">
+      <c r="C8" s="65">
+        <v>200</v>
+      </c>
+      <c r="D8" s="65">
+        <v>70</v>
+      </c>
+      <c r="E8" s="65">
+        <v>50</v>
+      </c>
+      <c r="F8" s="65">
+        <v>0</v>
+      </c>
+      <c r="G8" s="65">
+        <v>230</v>
+      </c>
+      <c r="H8" s="65">
+        <v>250</v>
+      </c>
+      <c r="I8" s="65">
+        <v>500</v>
+      </c>
+      <c r="J8" s="69">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13"/>
+        <v>32.5</v>
+      </c>
+      <c r="K8" s="66">
+        <v>23</v>
+      </c>
+      <c r="L8" s="67"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
@@ -19702,7 +19879,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -19710,27 +19887,43 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="68"/>
+      <c r="B9" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="15">
+      <c r="C9" s="65">
+        <v>75</v>
+      </c>
+      <c r="D9" s="65">
+        <v>50</v>
+      </c>
+      <c r="E9" s="65">
+        <v>50</v>
+      </c>
+      <c r="F9" s="65">
+        <v>0</v>
+      </c>
+      <c r="G9" s="65">
+        <v>181</v>
+      </c>
+      <c r="H9" s="65">
+        <v>206</v>
+      </c>
+      <c r="I9" s="65">
+        <v>233</v>
+      </c>
+      <c r="J9" s="69">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13"/>
+        <v>19.875</v>
+      </c>
+      <c r="K9" s="66">
+        <v>11</v>
+      </c>
+      <c r="L9" s="67"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>15</v>
@@ -19749,7 +19942,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -19757,27 +19950,43 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="68"/>
+      <c r="B10" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15">
+      <c r="C10" s="65">
+        <v>272</v>
+      </c>
+      <c r="D10" s="65">
+        <v>20</v>
+      </c>
+      <c r="E10" s="65">
+        <v>20</v>
+      </c>
+      <c r="F10" s="65">
+        <v>0</v>
+      </c>
+      <c r="G10" s="65">
+        <v>107</v>
+      </c>
+      <c r="H10" s="65">
+        <v>90</v>
+      </c>
+      <c r="I10" s="65">
+        <v>113</v>
+      </c>
+      <c r="J10" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13"/>
+        <v>15.55</v>
+      </c>
+      <c r="K10" s="66">
+        <v>8</v>
+      </c>
+      <c r="L10" s="67"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>16</v>
@@ -19796,7 +20005,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -19804,30 +20013,38 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="15">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65">
+        <v>10</v>
+      </c>
+      <c r="H11" s="65">
+        <v>10</v>
+      </c>
+      <c r="I11" s="65">
+        <v>40</v>
+      </c>
+      <c r="J11" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="66">
+        <v>1</v>
+      </c>
+      <c r="L11" s="67"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -19843,7 +20060,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -19851,30 +20068,44 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65">
+        <v>120</v>
+      </c>
+      <c r="E12" s="65">
+        <v>120</v>
+      </c>
+      <c r="F12" s="65">
+        <v>240</v>
+      </c>
+      <c r="G12" s="65">
+        <v>80</v>
+      </c>
+      <c r="H12" s="65">
+        <v>120</v>
+      </c>
+      <c r="I12" s="65">
+        <v>120</v>
+      </c>
+      <c r="J12" s="69">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13"/>
+      <c r="K12" s="66">
+        <v>2</v>
+      </c>
+      <c r="L12" s="67"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -19890,7 +20121,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -19898,21 +20129,22 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="52"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
       <c r="O13" s="11"/>
@@ -19938,41 +20170,42 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="73">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="25">
+        <v>547</v>
+      </c>
+      <c r="D14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25">
+        <v>260</v>
+      </c>
+      <c r="E14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="25">
+        <v>240</v>
+      </c>
+      <c r="F14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
+        <v>240</v>
+      </c>
+      <c r="G14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
+        <v>608</v>
+      </c>
+      <c r="H14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
+        <v>676</v>
+      </c>
+      <c r="I14" s="73">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
+        <v>1006</v>
+      </c>
+      <c r="J14" s="74">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
+        <v>3577</v>
+      </c>
+      <c r="K14" s="75"/>
+      <c r="L14" s="52"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
@@ -20010,7 +20243,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>89.424999999999997</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -20018,47 +20251,48 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>89.424999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="52"/>
+      <c r="B15" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="77">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="D15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
+        <v>6.5</v>
+      </c>
+      <c r="E15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
+        <v>6</v>
+      </c>
+      <c r="F15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
+        <v>6</v>
+      </c>
+      <c r="G15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
+        <v>15.2</v>
+      </c>
+      <c r="H15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="I15" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
+        <v>25.15</v>
+      </c>
+      <c r="J15" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="23"/>
+        <v>89.424999999999997</v>
+      </c>
+      <c r="K15" s="79"/>
+      <c r="L15" s="52"/>
       <c r="M15" s="1"/>
       <c r="N15" s="20" t="s">
         <v>19</v>
@@ -20098,7 +20332,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>2.2356249999999998</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -20106,8 +20340,22 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
-      </c>
+        <v>2.2356249999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -20531,7 +20779,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -20548,7 +20796,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -20578,7 +20826,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -20595,7 +20843,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -21252,7 +21500,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -21269,7 +21517,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -21299,7 +21547,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -21316,7 +21564,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -21973,7 +22221,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -21990,7 +22238,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -22020,7 +22268,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -22037,7 +22285,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -22694,7 +22942,7 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -22711,7 +22959,7 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -22741,7 +22989,7 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -22758,7 +23006,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218F41BE-2971-4B0B-A3AA-B6866C5B0A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC3C123-2803-41DB-81FE-FDE1CA0A15D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -550,32 +550,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -625,6 +601,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,103 +987,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="47" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="72"/>
+      <c r="Z4" s="72"/>
+      <c r="AA4" s="72"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1100,16 +1100,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1117,16 +1117,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1798,103 +1798,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1911,16 +1911,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1928,16 +1928,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2519,103 +2519,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2632,16 +2632,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2649,16 +2649,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3240,103 +3240,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3353,16 +3353,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3370,16 +3370,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3961,103 +3961,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4074,16 +4074,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4091,16 +4091,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4682,103 +4682,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4795,16 +4795,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4812,16 +4812,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5403,103 +5403,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5516,16 +5516,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5533,16 +5533,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6124,103 +6124,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6237,16 +6237,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6254,16 +6254,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6845,103 +6845,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6958,16 +6958,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6975,16 +6975,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7566,103 +7566,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7679,16 +7679,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7696,16 +7696,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8287,103 +8287,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8400,16 +8400,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8417,16 +8417,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9008,103 +9008,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9121,16 +9121,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9138,16 +9138,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9733,103 +9733,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9846,16 +9846,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9863,16 +9863,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -10454,103 +10454,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10567,16 +10567,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10584,16 +10584,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11175,103 +11175,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11288,16 +11288,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11305,16 +11305,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11896,103 +11896,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12009,16 +12009,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12026,16 +12026,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12617,103 +12617,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12730,16 +12730,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12747,16 +12747,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13338,103 +13338,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13451,16 +13451,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13468,16 +13468,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14059,103 +14059,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14172,16 +14172,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14189,16 +14189,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14780,103 +14780,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14893,16 +14893,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14910,16 +14910,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15501,103 +15501,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15614,16 +15614,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15631,16 +15631,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16222,103 +16222,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16335,16 +16335,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16352,16 +16352,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16943,103 +16943,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17056,16 +17056,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17073,16 +17073,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17726,103 +17726,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17839,16 +17839,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17856,16 +17856,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18411,16 +18411,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="51" t="s">
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -18789,103 +18789,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18902,16 +18902,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18919,16 +18919,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19067,7 +19067,7 @@
         <v>22.65</v>
       </c>
       <c r="W8" s="12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y8" s="39">
         <f>J8</f>
@@ -19580,18 +19580,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -19603,112 +19603,112 @@
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19720,39 +19720,39 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A6" s="52"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="56" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="52"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="47"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19760,38 +19760,38 @@
       <c r="AA6" s="18"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A7" s="60"/>
-      <c r="B7" s="61" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="63" t="s">
+      <c r="F7" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="65" t="s">
+      <c r="J7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="66" t="s">
+      <c r="K7" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="67"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="6"/>
       <c r="N7" s="7" t="s">
         <v>5</v>
@@ -19828,39 +19828,39 @@
       <c r="AA7" s="18"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A8" s="68"/>
-      <c r="B8" s="61" t="s">
+      <c r="A8" s="60"/>
+      <c r="B8" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="65">
+      <c r="C8" s="57">
         <v>200</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="57">
         <v>70</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="57">
         <v>50</v>
       </c>
-      <c r="F8" s="65">
-        <v>0</v>
-      </c>
-      <c r="G8" s="65">
+      <c r="F8" s="57">
+        <v>0</v>
+      </c>
+      <c r="G8" s="57">
         <v>230</v>
       </c>
-      <c r="H8" s="65">
+      <c r="H8" s="57">
         <v>250</v>
       </c>
-      <c r="I8" s="65">
+      <c r="I8" s="57">
         <v>500</v>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="61">
         <f>SUM(C8:I8)/40</f>
         <v>32.5</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="58">
         <v>23</v>
       </c>
-      <c r="L8" s="67"/>
+      <c r="L8" s="59"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
@@ -19891,39 +19891,39 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A9" s="68"/>
-      <c r="B9" s="61" t="s">
+      <c r="A9" s="60"/>
+      <c r="B9" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="65">
+      <c r="C9" s="57">
         <v>75</v>
       </c>
-      <c r="D9" s="65">
+      <c r="D9" s="57">
         <v>50</v>
       </c>
-      <c r="E9" s="65">
+      <c r="E9" s="57">
         <v>50</v>
       </c>
-      <c r="F9" s="65">
-        <v>0</v>
-      </c>
-      <c r="G9" s="65">
+      <c r="F9" s="57">
+        <v>0</v>
+      </c>
+      <c r="G9" s="57">
         <v>181</v>
       </c>
-      <c r="H9" s="65">
+      <c r="H9" s="57">
         <v>206</v>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="57">
         <v>233</v>
       </c>
-      <c r="J9" s="69">
+      <c r="J9" s="61">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>19.875</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="58">
         <v>11</v>
       </c>
-      <c r="L9" s="67"/>
+      <c r="L9" s="59"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>15</v>
@@ -19954,39 +19954,39 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A10" s="68"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="65">
+      <c r="C10" s="57">
         <v>272</v>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="57">
         <v>20</v>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="57">
         <v>20</v>
       </c>
-      <c r="F10" s="65">
-        <v>0</v>
-      </c>
-      <c r="G10" s="65">
+      <c r="F10" s="57">
+        <v>0</v>
+      </c>
+      <c r="G10" s="57">
         <v>107</v>
       </c>
-      <c r="H10" s="65">
+      <c r="H10" s="57">
         <v>90</v>
       </c>
-      <c r="I10" s="65">
+      <c r="I10" s="57">
         <v>113</v>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="61">
         <f t="shared" si="0"/>
         <v>15.55</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="58">
         <v>8</v>
       </c>
-      <c r="L10" s="67"/>
+      <c r="L10" s="59"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>16</v>
@@ -20017,31 +20017,31 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65">
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57">
         <v>10</v>
       </c>
-      <c r="H11" s="65">
+      <c r="H11" s="57">
         <v>10</v>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="57">
         <v>40</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="61">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="58">
         <v>1</v>
       </c>
-      <c r="L11" s="67"/>
+      <c r="L11" s="59"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>24</v>
@@ -20072,37 +20072,37 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71" t="s">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65">
+      <c r="C12" s="57"/>
+      <c r="D12" s="57">
         <v>120</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="57">
         <v>120</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="57">
         <v>240</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="57">
         <v>80</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="57">
         <v>120</v>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="57">
         <v>120</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="61">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="58">
         <v>2</v>
       </c>
-      <c r="L12" s="67"/>
+      <c r="L12" s="59"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>18</v>
@@ -20133,18 +20133,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="52"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="47"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
       <c r="O13" s="11"/>
@@ -20170,42 +20170,42 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="52"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="73">
+      <c r="A14" s="47"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="65">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
         <v>547</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="65">
         <f t="shared" si="5"/>
         <v>260</v>
       </c>
-      <c r="E14" s="73">
+      <c r="E14" s="65">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="F14" s="73">
+      <c r="F14" s="65">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="G14" s="73">
+      <c r="G14" s="65">
         <f t="shared" si="5"/>
         <v>608</v>
       </c>
-      <c r="H14" s="73">
+      <c r="H14" s="65">
         <f t="shared" si="5"/>
         <v>676</v>
       </c>
-      <c r="I14" s="73">
+      <c r="I14" s="65">
         <f t="shared" si="5"/>
         <v>1006</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="66">
         <f>SUM(C14:I14)</f>
         <v>3577</v>
       </c>
-      <c r="K14" s="75"/>
-      <c r="L14" s="52"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="47"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
@@ -20255,44 +20255,44 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="52"/>
-      <c r="B15" s="76" t="s">
+      <c r="A15" s="47"/>
+      <c r="B15" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="69">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
         <v>13.675000000000001</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="69">
         <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="69">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="69">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="G15" s="77">
+      <c r="G15" s="69">
         <f t="shared" si="7"/>
         <v>15.2</v>
       </c>
-      <c r="H15" s="77">
+      <c r="H15" s="69">
         <f t="shared" si="7"/>
         <v>16.899999999999999</v>
       </c>
-      <c r="I15" s="77">
+      <c r="I15" s="69">
         <f t="shared" si="7"/>
         <v>25.15</v>
       </c>
-      <c r="J15" s="78">
+      <c r="J15" s="70">
         <f t="shared" si="7"/>
         <v>89.424999999999997</v>
       </c>
-      <c r="K15" s="79"/>
-      <c r="L15" s="52"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="47"/>
       <c r="M15" s="1"/>
       <c r="N15" s="20" t="s">
         <v>19</v>
@@ -20344,18 +20344,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -20421,103 +20421,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20534,16 +20534,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20551,16 +20551,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21142,103 +21142,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21255,16 +21255,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21272,16 +21272,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21863,103 +21863,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21976,16 +21976,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21993,16 +21993,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22584,103 +22584,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="Y3" s="51" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22697,16 +22697,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22714,16 +22714,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="50" t="s">
+      <c r="P6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC3C123-2803-41DB-81FE-FDE1CA0A15D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BDF89D-7505-485F-B0BE-C7DADC3AEC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +226,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -446,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -552,52 +545,52 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -616,13 +609,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -19602,19 +19589,19 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
       <c r="K2" s="47"/>
       <c r="L2" s="47"/>
       <c r="M2" s="1"/>
@@ -19632,15 +19619,15 @@
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="47"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
       <c r="M3" s="1"/>
@@ -19661,15 +19648,15 @@
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
       <c r="M4" s="1"/>
@@ -19686,17 +19673,17 @@
       <c r="Z4" s="76"/>
       <c r="AA4" s="76"/>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47"/>
       <c r="M5" s="1"/>
@@ -19725,16 +19712,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -20108,28 +20095,45 @@
         <v>18</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>120</v>
+      </c>
+      <c r="R12" s="11">
+        <f>120+120</f>
+        <v>240</v>
+      </c>
+      <c r="S12" s="11">
+        <v>200</v>
+      </c>
+      <c r="T12" s="11">
+        <f>40+200</f>
+        <v>240</v>
+      </c>
+      <c r="U12" s="11">
+        <f>40+200</f>
+        <v>240</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20214,31 +20218,31 @@
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -20247,11 +20251,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>89.424999999999997</v>
+        <v>60.424999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20303,31 +20307,31 @@
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -20336,11 +20340,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>2.2356249999999998</v>
+        <v>1.5106249999999999</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
@@ -20640,18 +20644,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>136</v>
+      </c>
+      <c r="D8" s="11">
+        <v>46</v>
+      </c>
+      <c r="E8" s="11">
+        <v>46</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>81</v>
+      </c>
+      <c r="H8" s="11">
+        <v>66</v>
+      </c>
+      <c r="I8" s="11">
+        <v>121</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>12.4</v>
+      </c>
+      <c r="K8" s="12">
+        <v>16</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -20671,7 +20691,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -20679,7 +20699,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -20687,18 +20707,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>126</v>
+      </c>
+      <c r="D9" s="11">
+        <v>109</v>
+      </c>
+      <c r="E9" s="11">
+        <v>88</v>
+      </c>
+      <c r="F9" s="11">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11">
+        <v>78</v>
+      </c>
+      <c r="H9" s="11">
+        <v>73</v>
+      </c>
+      <c r="I9" s="11">
+        <v>78</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>14.175000000000001</v>
+      </c>
+      <c r="K9" s="12">
+        <v>7</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -20718,7 +20754,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -20726,7 +20762,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>14.175000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -20734,18 +20770,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>120</v>
+      </c>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>98</v>
+      </c>
+      <c r="H10" s="11">
+        <v>33</v>
+      </c>
+      <c r="I10" s="11">
+        <v>78</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>8.4749999999999996</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -20765,7 +20817,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -20773,7 +20825,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4749999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -20781,18 +20833,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>30</v>
+      </c>
+      <c r="D11" s="11">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>58</v>
+      </c>
+      <c r="F11" s="11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11">
+        <v>6</v>
+      </c>
+      <c r="I11" s="11">
+        <v>6</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>3.55</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -20812,7 +20880,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -20820,7 +20888,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -20828,18 +20896,34 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>280</v>
+      </c>
+      <c r="D12" s="11">
+        <v>200</v>
+      </c>
+      <c r="E12" s="11">
+        <v>200</v>
+      </c>
+      <c r="F12" s="11">
+        <v>200</v>
+      </c>
+      <c r="G12" s="11">
+        <v>360</v>
+      </c>
+      <c r="H12" s="11">
+        <v>360</v>
+      </c>
+      <c r="I12" s="11">
+        <v>400</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K12" s="12">
+        <v>3</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -20859,7 +20943,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -20867,7 +20951,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20911,35 +20995,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>3544</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -20979,7 +21063,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>88.6</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -20987,7 +21071,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20997,35 +21081,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.4250000000000007</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.6749999999999998</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.875</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.45</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.074999999999999</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>88.6</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -21067,7 +21151,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -21075,7 +21159,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>2.2149999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BDF89D-7505-485F-B0BE-C7DADC3AEC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30104B5-FE1A-4CCA-ADDD-E7E48135A1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="33">
   <si>
     <t>Booking</t>
   </si>
@@ -130,6 +130,30 @@
   </si>
   <si>
     <t>Jabbar</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday </t>
+  </si>
+  <si>
+    <t>Negotiate</t>
   </si>
 </sst>
 </file>
@@ -439,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -604,6 +628,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -953,7 +980,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1830,11 +1859,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -1857,9 +1886,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -2551,11 +2580,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -2578,9 +2607,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -3272,11 +3301,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -3299,9 +3328,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -3993,11 +4022,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -4020,9 +4049,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -4714,11 +4743,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -4741,9 +4770,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -5435,11 +5464,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -5462,9 +5491,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -6156,11 +6185,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -6183,9 +6212,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -6877,11 +6906,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -6904,9 +6933,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -7598,11 +7627,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -7625,9 +7654,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -8319,11 +8348,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -8346,9 +8375,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -8974,7 +9003,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -8983,7 +9014,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="L1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="76"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -9040,11 +9074,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -9067,9 +9101,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -9272,9 +9306,7 @@
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
-      <c r="K9" s="12">
-        <v>8</v>
-      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -9321,9 +9353,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="12">
-        <v>10</v>
-      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -9657,7 +9687,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -9765,11 +9796,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -9792,9 +9823,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -10486,11 +10517,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -10513,9 +10544,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -11207,11 +11238,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -11234,9 +11265,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -11928,11 +11959,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -11955,9 +11986,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -12649,11 +12680,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -12676,9 +12707,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -13370,11 +13401,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -13397,9 +13428,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -14091,11 +14122,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -14118,9 +14149,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -14812,11 +14843,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -14839,9 +14870,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -15533,11 +15564,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -15560,9 +15591,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -16254,11 +16285,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -16281,9 +16312,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -16909,7 +16940,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -16975,11 +17008,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -17002,9 +17035,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -17758,11 +17791,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -17785,9 +17818,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -18398,16 +18431,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -18755,7 +18788,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -18821,11 +18856,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -18848,9 +18883,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -19567,7 +19602,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="47"/>
+      <c r="A1" s="52" t="s">
+        <v>29</v>
+      </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="47"/>
@@ -19640,11 +19677,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
@@ -19669,9 +19706,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
@@ -19712,16 +19749,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -19852,29 +19889,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>200</v>
+      </c>
+      <c r="P8" s="11">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>205</v>
+      </c>
+      <c r="T8" s="11">
+        <v>210</v>
+      </c>
+      <c r="U8" s="11">
+        <v>165</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>22.5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>21</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>32.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>32.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -19915,29 +19968,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>75</v>
+      </c>
+      <c r="P9" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>50</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>170</v>
+      </c>
+      <c r="T9" s="11">
+        <v>200</v>
+      </c>
+      <c r="U9" s="11">
+        <v>250</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>19.875</v>
+      </c>
+      <c r="W9" s="12">
+        <v>11</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>19.875</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>19.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -19978,29 +20047,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>172</v>
+      </c>
+      <c r="P10" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>20</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>92</v>
+      </c>
+      <c r="T10" s="11">
+        <v>80</v>
+      </c>
+      <c r="U10" s="11">
+        <v>98</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>12.05</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>15.55</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>15.55</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -20214,15 +20299,15 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
@@ -20230,19 +20315,19 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>667</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>730</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>753</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>1160</v>
+        <v>3337</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -20251,11 +20336,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>29</v>
+        <v>83.424999999999997</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>60.424999999999997</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20303,15 +20388,15 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>11.175000000000001</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
@@ -20319,19 +20404,19 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>16.675000000000001</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>18.25</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>18.824999999999999</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>29</v>
+        <v>83.424999999999997</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -20340,11 +20425,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0.72499999999999998</v>
+        <v>2.0856249999999998</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.5106249999999999</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
@@ -20396,7 +20481,7 @@
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -20404,7 +20489,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -20470,11 +20557,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -20497,9 +20584,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -20677,29 +20764,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>96</v>
+      </c>
+      <c r="P8" s="11">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>26</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>41</v>
+      </c>
+      <c r="T8" s="11">
+        <v>26</v>
+      </c>
+      <c r="U8" s="11">
+        <v>81</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>7.4</v>
+      </c>
+      <c r="W8" s="12">
+        <v>13</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>12.4</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>12.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -20740,29 +20843,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>126</v>
+      </c>
+      <c r="P9" s="11">
+        <v>96</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>76</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>78</v>
+      </c>
+      <c r="T9" s="11">
+        <v>73</v>
+      </c>
+      <c r="U9" s="11">
+        <v>78</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>13.175000000000001</v>
+      </c>
+      <c r="W9" s="12">
+        <v>6</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>14.175000000000001</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>13.175000000000001</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>14.175000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -20803,29 +20922,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>120</v>
+      </c>
+      <c r="P10" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>98</v>
+      </c>
+      <c r="T10" s="11">
+        <v>33</v>
+      </c>
+      <c r="U10" s="11">
+        <v>78</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.4749999999999996</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>8.4749999999999996</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>8.4749999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -20866,7 +21001,9 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="11">
+        <v>12</v>
+      </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -20875,20 +21012,22 @@
       <c r="U11" s="11"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>0.3</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>3.55</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -20925,33 +21064,51 @@
         <v>3</v>
       </c>
       <c r="L12" s="13"/>
-      <c r="M12" s="16"/>
+      <c r="M12" s="16" t="s">
+        <v>32</v>
+      </c>
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>280</v>
+      </c>
+      <c r="P12" s="11">
+        <v>638</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>480</v>
+      </c>
+      <c r="R12" s="11">
+        <v>679</v>
+      </c>
+      <c r="S12" s="11">
+        <v>760</v>
+      </c>
+      <c r="T12" s="11">
+        <v>640</v>
+      </c>
+      <c r="U12" s="11">
+        <v>1078</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>113.875</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>113.875</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>-63.875</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -21030,35 +21187,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>679</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1315</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>5729</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -21067,11 +21224,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>143.22499999999999</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>88.6</v>
+        <v>-54.625</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21118,35 +21275,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>15.85</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.55</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.975000000000001</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24.425000000000001</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>32.875</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>143.22499999999999</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -21155,11 +21312,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>3.5806249999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>2.2149999999999999</v>
+        <v>-1.3656250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21271,11 +21428,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -21298,9 +21455,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -21445,18 +21602,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>142</v>
+      </c>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>60</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>117</v>
+      </c>
+      <c r="H8" s="11">
+        <v>106</v>
+      </c>
+      <c r="I8" s="11">
+        <v>297</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>18.55</v>
+      </c>
+      <c r="K8" s="12">
+        <v>14</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -21476,7 +21649,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>18.55</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -21484,7 +21657,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21492,18 +21665,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>42</v>
+      </c>
+      <c r="D9" s="11">
+        <v>58</v>
+      </c>
+      <c r="E9" s="11">
+        <v>31</v>
+      </c>
+      <c r="F9" s="11">
+        <v>101</v>
+      </c>
+      <c r="G9" s="11">
+        <v>54</v>
+      </c>
+      <c r="H9" s="11">
+        <v>78</v>
+      </c>
+      <c r="I9" s="11">
+        <v>64</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10.7</v>
+      </c>
+      <c r="K9" s="12">
+        <v>11</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -21523,7 +21712,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -21531,7 +21720,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -21539,18 +21728,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>32</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>35</v>
+      </c>
+      <c r="H10" s="11">
+        <v>25</v>
+      </c>
+      <c r="I10" s="11">
+        <v>108</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -21570,7 +21775,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -21578,7 +21783,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21586,18 +21791,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>98</v>
+      </c>
+      <c r="D11" s="11">
+        <v>24</v>
+      </c>
+      <c r="E11" s="11">
+        <v>24</v>
+      </c>
+      <c r="F11" s="11">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11">
+        <v>39</v>
+      </c>
+      <c r="H11" s="11">
+        <v>26</v>
+      </c>
+      <c r="I11" s="11">
+        <v>33</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6.7</v>
+      </c>
+      <c r="K11" s="12">
+        <v>6</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -21617,7 +21838,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -21625,7 +21846,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21634,17 +21855,31 @@
         <v>17</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>600</v>
+      </c>
+      <c r="E12" s="11">
+        <v>640</v>
+      </c>
+      <c r="F12" s="11">
+        <v>360</v>
+      </c>
+      <c r="G12" s="11">
+        <v>480</v>
+      </c>
+      <c r="H12" s="11">
+        <v>380</v>
+      </c>
+      <c r="I12" s="11">
+        <v>760</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>80.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>3</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -21664,7 +21899,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -21672,7 +21907,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -21716,35 +21951,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1262</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>4858</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -21784,7 +22019,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>121.45</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -21792,7 +22027,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21802,35 +22037,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.55</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>18.125</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.375</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31.55</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>121.45</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -21872,7 +22107,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>3.0362499999999999</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -21880,7 +22115,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>3.0362499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -21992,11 +22227,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -22019,9 +22254,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -22713,11 +22948,11 @@
       <c r="T3" s="73"/>
       <c r="U3" s="73"/>
       <c r="V3" s="73"/>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -22740,9 +22975,9 @@
       <c r="T4" s="73"/>
       <c r="U4" s="73"/>
       <c r="V4" s="73"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30104B5-FE1A-4CCA-ADDD-E7E48135A1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49770A0-459B-4F4A-AF98-432B27B0DD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="34">
   <si>
     <t>Booking</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Negotiate</t>
+  </si>
+  <si>
+    <t>Sohail SD</t>
   </si>
 </sst>
 </file>
@@ -275,7 +278,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +306,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -618,6 +627,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1003,103 +1016,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="72" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
+      <c r="Z3" s="74"/>
+      <c r="AA3" s="74"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="72"/>
-      <c r="AA4" s="72"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="74"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1116,16 +1129,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1133,16 +1146,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1814,103 +1827,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1927,16 +1940,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1944,16 +1957,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2535,103 +2548,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2648,16 +2661,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2665,16 +2678,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3256,103 +3269,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3369,16 +3382,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3386,16 +3399,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3977,103 +3990,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4090,16 +4103,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4107,16 +4120,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4698,103 +4711,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4811,16 +4824,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4828,16 +4841,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5419,103 +5432,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5532,16 +5545,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5549,16 +5562,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6140,103 +6153,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6253,16 +6266,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6270,16 +6283,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6861,103 +6874,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6974,16 +6987,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6991,16 +7004,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7582,103 +7595,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7695,16 +7708,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7712,16 +7725,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8303,103 +8316,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8416,16 +8429,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8433,16 +8446,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9014,10 +9027,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="76" t="s">
+      <c r="L1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="76"/>
+      <c r="M1" s="78"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -9029,103 +9042,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9142,16 +9155,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9159,16 +9172,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9751,103 +9764,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9864,16 +9877,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9881,16 +9894,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -10472,103 +10485,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10585,16 +10598,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10602,16 +10615,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11193,103 +11206,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11306,16 +11319,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11323,16 +11336,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11914,103 +11927,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12027,16 +12040,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12044,16 +12057,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12635,103 +12648,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12748,16 +12761,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12765,16 +12778,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13356,103 +13369,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13469,16 +13482,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13486,16 +13499,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14077,103 +14090,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14190,16 +14203,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14207,16 +14220,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14798,103 +14811,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14911,16 +14924,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14928,16 +14941,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15519,103 +15532,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15632,16 +15645,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15649,16 +15662,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16240,103 +16253,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16353,16 +16366,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16370,16 +16383,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16963,103 +16976,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17076,16 +17089,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17093,16 +17106,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17746,103 +17759,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17859,16 +17872,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17876,16 +17889,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18431,16 +18444,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="77" t="s">
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -18811,103 +18824,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18924,16 +18937,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18941,16 +18954,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19628,111 +19641,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="K2" s="47"/>
       <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="47"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19749,16 +19762,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -19767,16 +19780,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20482,7 +20495,7 @@
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.453125" customWidth="1"/>
+    <col min="22" max="22" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6.453125" bestFit="1" customWidth="1"/>
@@ -20512,103 +20525,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20625,16 +20638,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20642,16 +20655,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20752,7 +20765,7 @@
       <c r="I8" s="11">
         <v>121</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="73">
         <f>SUM(C8:I8)/40</f>
         <v>12.4</v>
       </c>
@@ -20785,7 +20798,7 @@
       <c r="U8" s="11">
         <v>81</v>
       </c>
-      <c r="V8" s="15">
+      <c r="V8" s="73">
         <f>SUM(O8:U8)/40</f>
         <v>7.4</v>
       </c>
@@ -20831,7 +20844,7 @@
       <c r="I9" s="11">
         <v>78</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="73">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>14.175000000000001</v>
       </c>
@@ -20864,8 +20877,8 @@
       <c r="U9" s="11">
         <v>78</v>
       </c>
-      <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+      <c r="V9" s="73">
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>13.175000000000001</v>
       </c>
       <c r="W9" s="12">
@@ -20910,7 +20923,7 @@
       <c r="I10" s="11">
         <v>78</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="73">
         <f t="shared" si="0"/>
         <v>8.4749999999999996</v>
       </c>
@@ -20943,7 +20956,7 @@
       <c r="U10" s="11">
         <v>78</v>
       </c>
-      <c r="V10" s="15">
+      <c r="V10" s="73">
         <f t="shared" si="1"/>
         <v>8.4749999999999996</v>
       </c>
@@ -20989,7 +21002,7 @@
       <c r="I11" s="11">
         <v>6</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="73">
         <f t="shared" si="0"/>
         <v>3.55</v>
       </c>
@@ -21010,7 +21023,7 @@
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="V11" s="73">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
@@ -21056,7 +21069,7 @@
       <c r="I12" s="11">
         <v>400</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="73">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -21091,7 +21104,7 @@
       <c r="U12" s="11">
         <v>1078</v>
       </c>
-      <c r="V12" s="15">
+      <c r="V12" s="73">
         <f t="shared" si="1"/>
         <v>113.875</v>
       </c>
@@ -21121,30 +21134,45 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
+      <c r="J13" s="73"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
+      <c r="N13" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="11">
+        <v>1600</v>
+      </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="S13" s="11">
+        <v>600</v>
+      </c>
+      <c r="T13" s="11">
+        <v>800</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1000</v>
+      </c>
+      <c r="V13" s="73">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -21187,7 +21215,7 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>634</v>
+        <v>2234</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
@@ -21203,19 +21231,19 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>977</v>
+        <v>1577</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>772</v>
+        <v>1572</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>1315</v>
+        <v>2315</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>5729</v>
+        <v>9729</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -21224,11 +21252,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>143.22499999999999</v>
+        <v>243.22499999999999</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>-54.625</v>
+        <v>-154.625</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21275,7 +21303,7 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>15.85</v>
+        <v>55.85</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
@@ -21291,19 +21319,19 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>24.425000000000001</v>
+        <v>39.424999999999997</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>19.3</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>32.875</v>
-      </c>
-      <c r="V15" s="22">
+        <v>57.875</v>
+      </c>
+      <c r="V15" s="72">
         <f t="shared" si="8"/>
-        <v>143.22499999999999</v>
+        <v>243.22499999999999</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -21312,11 +21340,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>3.5806249999999999</v>
+        <v>6.0806249999999995</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>-1.3656250000000001</v>
+        <v>-3.8656250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21383,103 +21411,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21496,16 +21524,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21513,16 +21541,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21635,29 +21663,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>142</v>
+      </c>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>60</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>117</v>
+      </c>
+      <c r="T8" s="11">
+        <v>106</v>
+      </c>
+      <c r="U8" s="11">
+        <v>297</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>18.55</v>
+      </c>
+      <c r="W8" s="12">
+        <v>14</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>18.55</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>18.55</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>18.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21761,29 +21805,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>20</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>35</v>
+      </c>
+      <c r="T10" s="11">
+        <v>15</v>
+      </c>
+      <c r="U10" s="11">
+        <v>90</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21824,29 +21884,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>98</v>
+      </c>
+      <c r="P11" s="11">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>18</v>
+      </c>
+      <c r="R11" s="11">
+        <v>18</v>
+      </c>
+      <c r="S11" s="11">
+        <v>24</v>
+      </c>
+      <c r="T11" s="11">
+        <v>16</v>
+      </c>
+      <c r="U11" s="11">
+        <v>18</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5.25</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>6.7</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>6.7</v>
+        <v>1.4500000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21986,35 +22062,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -22023,11 +22099,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>121.45</v>
+        <v>93.65</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22074,35 +22150,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.4249999999999998</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.125</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -22111,11 +22187,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.69500000000000006</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>3.0362499999999999</v>
+        <v>2.3412500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22182,103 +22258,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22295,16 +22371,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22312,16 +22388,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22448,18 +22524,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11">
+        <v>13</v>
+      </c>
+      <c r="E9" s="11">
+        <v>12</v>
+      </c>
+      <c r="F9" s="11">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11">
+        <v>50</v>
+      </c>
+      <c r="H9" s="11">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>3</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -22479,7 +22571,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -22487,7 +22579,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22542,18 +22634,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>82</v>
+      </c>
+      <c r="D11" s="11">
+        <v>25</v>
+      </c>
+      <c r="E11" s="11">
+        <v>25</v>
+      </c>
+      <c r="F11" s="11">
+        <v>52</v>
+      </c>
+      <c r="G11" s="11">
+        <v>53</v>
+      </c>
+      <c r="H11" s="11">
+        <v>42</v>
+      </c>
+      <c r="I11" s="11">
+        <v>44</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>8.0749999999999993</v>
+      </c>
+      <c r="K11" s="12">
+        <v>8</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -22573,7 +22681,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.0749999999999993</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -22581,7 +22689,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.0749999999999993</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22590,17 +22698,31 @@
         <v>17</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>160</v>
+      </c>
+      <c r="E12" s="11">
+        <v>320</v>
+      </c>
+      <c r="F12" s="11">
+        <v>300</v>
+      </c>
+      <c r="G12" s="11">
+        <v>400</v>
+      </c>
+      <c r="H12" s="11">
+        <v>200</v>
+      </c>
+      <c r="I12" s="11">
+        <v>520</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>47.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -22620,7 +22742,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -22628,7 +22750,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22672,35 +22794,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>2423</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -22740,7 +22862,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>60.575000000000003</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -22748,7 +22870,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>60.575000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22758,35 +22880,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.9250000000000007</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.1750000000000007</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.574999999999999</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.35</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>60.575000000000003</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -22828,7 +22950,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>1.514375</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -22836,7 +22958,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.514375</v>
       </c>
     </row>
   </sheetData>
@@ -22903,103 +23025,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="Y3" s="77" t="s">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="Y3" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -23016,16 +23138,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23033,16 +23155,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75" t="s">
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49770A0-459B-4F4A-AF98-432B27B0DD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444DD01-31FC-4420-8313-2070E50ABAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -631,6 +631,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1016,103 +1017,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="74" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
+      <c r="Z3" s="75"/>
+      <c r="AA3" s="75"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AA4" s="75"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1129,16 +1130,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1146,16 +1147,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1786,8 +1787,7 @@
     <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
@@ -1827,103 +1827,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1940,16 +1940,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1957,16 +1957,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2046,18 +2046,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>110</v>
+      </c>
+      <c r="D8" s="11">
+        <v>80</v>
+      </c>
+      <c r="E8" s="11">
+        <v>80</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>220</v>
+      </c>
+      <c r="H8" s="11">
+        <v>220</v>
+      </c>
+      <c r="I8" s="11">
+        <v>240</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>23.75</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -2077,7 +2093,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -2085,7 +2101,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2093,18 +2109,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>120</v>
+      </c>
+      <c r="D9" s="11">
+        <v>60</v>
+      </c>
+      <c r="E9" s="11">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>55</v>
+      </c>
+      <c r="H9" s="11">
+        <v>55</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="K9" s="12">
+        <v>3</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -2124,7 +2156,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -2132,7 +2164,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2140,18 +2172,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>452</v>
+      </c>
+      <c r="D10" s="11">
+        <v>292</v>
+      </c>
+      <c r="E10" s="11">
+        <v>252</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>272</v>
+      </c>
+      <c r="H10" s="11">
+        <v>264</v>
+      </c>
+      <c r="I10" s="11">
+        <v>312</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>46.1</v>
+      </c>
+      <c r="K10" s="12">
+        <v>10</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -2171,7 +2219,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>46.1</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -2179,7 +2227,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -2235,17 +2283,37 @@
         <v>17</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <f>80+120+40+120+80</f>
+        <v>440</v>
+      </c>
+      <c r="E12" s="11">
+        <f>80+120+80+360+80</f>
+        <v>720</v>
+      </c>
+      <c r="F12" s="11">
+        <f>80+120+760+120</f>
+        <v>1080</v>
+      </c>
+      <c r="G12" s="11">
+        <f>80+80+40+440</f>
+        <v>640</v>
+      </c>
+      <c r="H12" s="11">
+        <f>80+80+80+560</f>
+        <v>800</v>
+      </c>
+      <c r="I12" s="11">
+        <f>80+80+40+840+80</f>
+        <v>1120</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>120</v>
+      </c>
+      <c r="K12" s="12">
+        <v>9</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -2265,7 +2333,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -2273,7 +2341,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2317,35 +2385,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>682</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1339</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1722</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>7954</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -2385,7 +2453,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>198.85</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -2393,7 +2461,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>198.85</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2403,35 +2471,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>17.05</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>29.675000000000001</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>33.475000000000001</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>43.05</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>198.85</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -2473,7 +2541,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>4.9712499999999995</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -2481,7 +2549,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>4.9712499999999995</v>
       </c>
     </row>
   </sheetData>
@@ -2548,103 +2616,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2661,16 +2729,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2678,16 +2746,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3269,103 +3337,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3382,16 +3450,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3399,16 +3467,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3990,103 +4058,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4103,16 +4171,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4120,16 +4188,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4711,103 +4779,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4824,16 +4892,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4841,16 +4909,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5432,103 +5500,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5545,16 +5613,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5562,16 +5630,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6153,103 +6221,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6266,16 +6334,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6283,16 +6351,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6874,103 +6942,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6987,16 +7055,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7004,16 +7072,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7595,103 +7663,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7708,16 +7776,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7725,16 +7793,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8316,103 +8384,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8429,16 +8497,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8446,16 +8514,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9027,10 +9095,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="78" t="s">
+      <c r="L1" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="78"/>
+      <c r="M1" s="79"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -9042,103 +9110,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9155,16 +9223,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9172,16 +9240,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9764,103 +9832,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9877,16 +9945,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9894,16 +9962,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -10485,103 +10553,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10598,16 +10666,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10615,16 +10683,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11206,103 +11274,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11319,16 +11387,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11336,16 +11404,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11927,103 +11995,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12040,16 +12108,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12057,16 +12125,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12648,103 +12716,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12761,16 +12829,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12778,16 +12846,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13369,103 +13437,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13482,16 +13550,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13499,16 +13567,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14090,103 +14158,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14203,16 +14271,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14220,16 +14288,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14811,103 +14879,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14924,16 +14992,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14941,16 +15009,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15532,103 +15600,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15645,16 +15713,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15662,16 +15730,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16253,103 +16321,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16366,16 +16434,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16383,16 +16451,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16976,103 +17044,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17089,16 +17157,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17106,16 +17174,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17759,103 +17827,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17872,16 +17940,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17889,16 +17957,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18444,16 +18512,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="79" t="s">
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -18824,103 +18892,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18937,16 +19005,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18954,16 +19022,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19641,111 +19709,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="K2" s="47"/>
       <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="47"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19762,16 +19830,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80" t="s">
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -19780,16 +19848,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20525,103 +20593,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20638,16 +20706,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20655,16 +20723,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21411,103 +21479,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21524,16 +21592,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21541,16 +21609,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21961,29 +22029,45 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>3</v>
+      </c>
+      <c r="P12" s="11">
+        <v>281</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>403</v>
+      </c>
+      <c r="R12" s="11">
+        <v>161</v>
+      </c>
+      <c r="S12" s="11">
+        <v>383</v>
+      </c>
+      <c r="T12" s="11">
+        <v>281</v>
+      </c>
+      <c r="U12" s="11">
+        <v>561</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>51.825000000000003</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>80.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>51.825000000000003</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>80.5</v>
+        <v>28.674999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22062,35 +22146,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>38</v>
+        <v>319</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>78</v>
+        <v>481</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>176</v>
+        <v>559</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>137</v>
+        <v>418</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>405</v>
+        <v>966</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>1112</v>
+        <v>3185</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -22099,11 +22183,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>27.8</v>
+        <v>79.625</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>93.65</v>
+        <v>41.824999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22150,35 +22234,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>6.5</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0.95</v>
+        <v>7.9749999999999996</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>1.95</v>
+        <v>12.025</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0.45</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>4.4000000000000004</v>
+        <v>13.975</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>3.4249999999999998</v>
+        <v>10.45</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>10.125</v>
+        <v>24.15</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>27.8</v>
+        <v>79.625</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -22187,11 +22271,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0.69500000000000006</v>
+        <v>1.9906250000000001</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>2.3412500000000001</v>
+        <v>1.0456249999999998</v>
       </c>
     </row>
   </sheetData>
@@ -22225,11 +22309,10 @@
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -22258,103 +22341,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22371,16 +22454,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22388,16 +22471,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22557,29 +22640,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
+      <c r="P9" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>50</v>
+      </c>
+      <c r="S9" s="11">
+        <v>50</v>
+      </c>
+      <c r="T9" s="11">
+        <v>50</v>
+      </c>
+      <c r="U9" s="11">
+        <v>10</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>4.3</v>
+      </c>
+      <c r="W9" s="12">
+        <v>3</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>5</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>5</v>
+        <v>0.70000000000000018</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22667,29 +22766,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>16</v>
+      </c>
+      <c r="P11" s="11">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>21</v>
+      </c>
+      <c r="R11" s="11">
+        <v>22</v>
+      </c>
+      <c r="S11" s="11">
+        <v>15</v>
+      </c>
+      <c r="T11" s="11">
+        <v>10</v>
+      </c>
+      <c r="U11" s="11">
+        <v>15</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>8.0749999999999993</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>8.0749999999999993</v>
+        <v>5.0749999999999993</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22728,29 +22843,45 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>120</v>
+      </c>
+      <c r="P12" s="11">
+        <v>864</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1004</v>
+      </c>
+      <c r="R12" s="11">
+        <v>3399</v>
+      </c>
+      <c r="S12" s="11">
+        <v>1158</v>
+      </c>
+      <c r="T12" s="11">
+        <v>1436</v>
+      </c>
+      <c r="U12" s="11">
+        <v>2720</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>267.52499999999998</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>267.52499999999998</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>47.5</v>
+        <v>-220.02499999999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22829,35 +22960,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3471</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2745</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>10993</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -22866,11 +22997,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>274.82499999999999</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>60.575000000000003</v>
+        <v>-214.24999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22917,35 +23048,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.625</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>86.775000000000006</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30.574999999999999</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.4</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68.625</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>274.82499999999999</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -22954,11 +23085,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>6.8706249999999995</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.514375</v>
+        <v>-5.3562499999999993</v>
       </c>
     </row>
   </sheetData>
@@ -23025,103 +23156,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
+      <c r="B2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="Y3" s="79" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="Y3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -23138,16 +23269,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23155,16 +23286,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -23244,14 +23375,14 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="15">
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="74">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
       </c>
@@ -23261,14 +23392,14 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="74">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
@@ -23291,14 +23422,14 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="15">
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="74">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
@@ -23308,14 +23439,14 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="74">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
@@ -23338,14 +23469,14 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15">
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -23355,14 +23486,14 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23385,14 +23516,14 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="15">
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -23402,14 +23533,14 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23432,14 +23563,14 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15">
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="74">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -23449,14 +23580,14 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23477,25 +23608,25 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="74"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="74"/>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444DD01-31FC-4420-8313-2070E50ABAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795C3C20-925C-4ADE-B78B-2EEB2C7E903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="36">
   <si>
     <t>Booking</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>Sohail SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabran </t>
+  </si>
+  <si>
+    <t>Shahid SB</t>
   </si>
 </sst>
 </file>
@@ -2079,29 +2085,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>110</v>
+      </c>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>80</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>220</v>
+      </c>
+      <c r="T8" s="11">
+        <v>220</v>
+      </c>
+      <c r="U8" s="11">
+        <v>240</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>23.75</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>23.75</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>23.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2142,29 +2164,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>90</v>
+      </c>
+      <c r="P9" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>55</v>
+      </c>
+      <c r="T9" s="11">
+        <v>55</v>
+      </c>
+      <c r="U9" s="11">
+        <v>50</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>8.25</v>
+      </c>
+      <c r="W9" s="12">
+        <v>2</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>9</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2205,29 +2243,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>452</v>
+      </c>
+      <c r="P10" s="11">
+        <v>292</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>252</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>272</v>
+      </c>
+      <c r="T10" s="11">
+        <v>264</v>
+      </c>
+      <c r="U10" s="11">
+        <v>312</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>46.1</v>
+      </c>
+      <c r="W10" s="12">
+        <v>10</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>46.1</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46.1</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>46.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -2320,28 +2374,42 @@
         <v>18</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>440</v>
+      </c>
+      <c r="R12" s="11">
+        <v>760</v>
+      </c>
+      <c r="S12" s="11">
+        <v>400</v>
+      </c>
+      <c r="T12" s="11">
+        <v>520</v>
+      </c>
+      <c r="U12" s="11">
+        <v>800</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>78</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2357,11 +2425,19 @@
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>35</v>
+      </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
+      <c r="P13" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>20</v>
+      </c>
+      <c r="R13" s="11">
+        <v>10</v>
+      </c>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
@@ -2420,35 +2496,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1402</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>6284</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -2457,11 +2533,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>156.1</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>198.85</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2508,35 +2584,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.05</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.675000000000001</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>26.475000000000001</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>157.1</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -2545,11 +2621,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>3.9024999999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>4.9712499999999995</v>
+        <v>1.0687500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2835,46 +2911,76 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>198</v>
+      </c>
+      <c r="D8" s="11">
+        <v>56</v>
+      </c>
+      <c r="E8" s="11">
+        <v>56</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>61</v>
+      </c>
+      <c r="H8" s="11">
+        <v>54</v>
+      </c>
+      <c r="I8" s="11">
+        <v>63</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>12.2</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
+      <c r="O8" s="11">
+        <v>196</v>
+      </c>
+      <c r="P8" s="11">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>53</v>
+      </c>
       <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="S8" s="11">
+        <v>58</v>
+      </c>
+      <c r="T8" s="11">
+        <v>53</v>
+      </c>
+      <c r="U8" s="11">
+        <v>56</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11.8</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>0.39999999999999858</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2882,42 +2988,74 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11">
+        <v>19</v>
+      </c>
+      <c r="E9" s="11">
+        <v>18</v>
+      </c>
+      <c r="F9" s="11">
+        <v>21</v>
+      </c>
+      <c r="G9" s="11">
+        <v>146</v>
+      </c>
+      <c r="H9" s="11">
+        <v>86</v>
+      </c>
+      <c r="I9" s="11">
+        <v>186</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>12.2</v>
+      </c>
+      <c r="K9" s="12">
+        <v>8</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>12</v>
+      </c>
+      <c r="P9" s="11">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>18</v>
+      </c>
+      <c r="R9" s="11">
+        <v>21</v>
+      </c>
+      <c r="S9" s="11">
+        <v>146</v>
+      </c>
+      <c r="T9" s="11">
+        <v>86</v>
+      </c>
+      <c r="U9" s="11">
+        <v>186</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
+        <v>12.2</v>
+      </c>
+      <c r="W9" s="12">
+        <v>8</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
@@ -2929,42 +3067,74 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>160</v>
+      </c>
+      <c r="D10" s="11">
+        <v>72</v>
+      </c>
+      <c r="E10" s="11">
+        <v>72</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>200</v>
+      </c>
+      <c r="H10" s="11">
+        <v>40</v>
+      </c>
+      <c r="I10" s="11">
+        <v>180</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>160</v>
+      </c>
+      <c r="P10" s="11">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>72</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>200</v>
+      </c>
+      <c r="T10" s="11">
+        <v>40</v>
+      </c>
+      <c r="U10" s="11">
+        <v>180</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
@@ -2976,46 +3146,66 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="C11" s="11">
+        <v>96</v>
+      </c>
+      <c r="D11" s="11">
+        <v>74</v>
+      </c>
+      <c r="E11" s="11">
+        <v>74</v>
+      </c>
+      <c r="F11" s="11">
+        <v>74</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>7.95</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="O11" s="11">
+        <v>84</v>
+      </c>
+      <c r="P11" s="11">
+        <v>74</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>74</v>
+      </c>
+      <c r="R11" s="11">
+        <v>74</v>
+      </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.65</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.29999999999999982</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -3023,82 +3213,146 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>240</v>
+      </c>
+      <c r="D12" s="11">
+        <v>640</v>
+      </c>
+      <c r="E12" s="11">
+        <v>440</v>
+      </c>
+      <c r="F12" s="11">
+        <v>840</v>
+      </c>
+      <c r="G12" s="11">
+        <v>540</v>
+      </c>
+      <c r="H12" s="11">
+        <v>400</v>
+      </c>
+      <c r="I12" s="11">
+        <v>800</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>97.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>79</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>120</v>
+      </c>
+      <c r="R12" s="11">
+        <v>120</v>
+      </c>
+      <c r="S12" s="11">
+        <v>160</v>
+      </c>
+      <c r="T12" s="11">
+        <v>200</v>
+      </c>
+      <c r="U12" s="11">
+        <v>160</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>20.975000000000001</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20.975000000000001</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76.525000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
+      <c r="B13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="11">
+        <v>20</v>
+      </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="G13" s="11">
+        <v>10</v>
+      </c>
+      <c r="H13" s="11">
+        <v>10</v>
+      </c>
+      <c r="I13" s="11">
+        <v>40</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K13" s="18">
+        <v>2</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="N13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="11">
+        <v>20</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
       <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="S13" s="11">
+        <v>10</v>
+      </c>
+      <c r="T13" s="11">
+        <v>10</v>
+      </c>
+      <c r="U13" s="11">
+        <v>20</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -3106,83 +3360,83 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>861</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>957</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1269</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>5998</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>2889</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>149.94999999999999</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>72.224999999999994</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>77.725000000000009</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3192,35 +3446,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21.524999999999999</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.375</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.925000000000001</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31.725000000000001</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>149.94999999999999</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -3229,48 +3483,48 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.4250000000000007</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.7249999999999996</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.05</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72.224999999999994</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>3.7487499999999998</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>1.8056249999999998</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.9431250000000002</v>
       </c>
     </row>
   </sheetData>
@@ -3556,18 +3810,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>160</v>
+      </c>
+      <c r="D8" s="11">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>55</v>
+      </c>
+      <c r="H8" s="11">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11">
+        <v>65</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>10.5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>11</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -3587,7 +3857,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -3595,7 +3865,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -3603,18 +3873,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>22</v>
+      </c>
+      <c r="D9" s="11">
+        <v>6</v>
+      </c>
+      <c r="E9" s="11">
+        <v>6</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>80</v>
+      </c>
+      <c r="H9" s="11">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>5.6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>9</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -3634,7 +3920,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -3642,7 +3928,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -3650,18 +3936,32 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="C10" s="11">
+        <v>160</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11">
+        <v>126</v>
+      </c>
+      <c r="H10" s="11">
+        <v>44</v>
+      </c>
+      <c r="I10" s="11">
+        <v>134</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>11.6</v>
+      </c>
+      <c r="K10" s="12">
+        <v>10</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -3681,7 +3981,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -3689,7 +3989,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -3697,18 +3997,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="11">
+        <v>6</v>
+      </c>
+      <c r="F11" s="11">
+        <v>6</v>
+      </c>
+      <c r="G11" s="11">
+        <v>6</v>
+      </c>
+      <c r="H11" s="11">
+        <v>6</v>
+      </c>
+      <c r="I11" s="11">
+        <v>6</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="K11" s="12">
+        <v>1</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -3728,7 +4044,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -3736,7 +4052,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -3744,18 +4060,34 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>240</v>
+      </c>
+      <c r="D12" s="11">
+        <v>640</v>
+      </c>
+      <c r="E12" s="11">
+        <v>440</v>
+      </c>
+      <c r="F12" s="11">
+        <v>840</v>
+      </c>
+      <c r="G12" s="11">
+        <v>540</v>
+      </c>
+      <c r="H12" s="11">
+        <v>400</v>
+      </c>
+      <c r="I12" s="11">
+        <v>800</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>97.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>10</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -3775,7 +4107,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -3783,21 +4115,42 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="B13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="11">
+        <v>24</v>
+      </c>
+      <c r="D13" s="11">
+        <v>16</v>
+      </c>
+      <c r="E13" s="11">
+        <v>16</v>
+      </c>
+      <c r="F13" s="11">
+        <v>4</v>
+      </c>
+      <c r="G13" s="11">
+        <v>4</v>
+      </c>
+      <c r="H13" s="11">
+        <v>4</v>
+      </c>
+      <c r="I13" s="11">
+        <v>4</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8</v>
+      </c>
+      <c r="K13" s="12">
+        <v>2</v>
+      </c>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
       <c r="O13" s="11"/>
@@ -3811,7 +4164,7 @@
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -3819,7 +4172,7 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -3827,35 +4180,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>5117</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -3895,7 +4248,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>127.925</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -3903,7 +4256,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>127.925</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3913,35 +4266,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>15.175000000000001</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21.25</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.274999999999999</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26.725000000000001</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>127.925</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -3983,7 +4336,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>3.1981250000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -3991,7 +4344,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>3.1981250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22033,7 +22386,8 @@
         <v>3</v>
       </c>
       <c r="P12" s="11">
-        <v>281</v>
+        <f>281-40</f>
+        <v>241</v>
       </c>
       <c r="Q12" s="11">
         <v>403</v>
@@ -22042,17 +22396,20 @@
         <v>161</v>
       </c>
       <c r="S12" s="11">
-        <v>383</v>
+        <f>383-20</f>
+        <v>363</v>
       </c>
       <c r="T12" s="11">
-        <v>281</v>
+        <f>281-20</f>
+        <v>261</v>
       </c>
       <c r="U12" s="11">
-        <v>561</v>
+        <f>561-20</f>
+        <v>541</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>51.825000000000003</v>
+        <v>49.325000000000003</v>
       </c>
       <c r="W12" s="12">
         <v>3</v>
@@ -22063,11 +22420,11 @@
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>51.825000000000003</v>
+        <v>49.325000000000003</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>28.674999999999997</v>
+        <v>31.174999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22150,7 +22507,7 @@
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
@@ -22162,19 +22519,19 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>3185</v>
+        <v>3085</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -22183,11 +22540,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>79.625</v>
+        <v>77.125</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>41.824999999999996</v>
+        <v>44.324999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22238,7 +22595,7 @@
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>7.9749999999999996</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
@@ -22250,19 +22607,19 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>13.975</v>
+        <v>13.475</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>10.45</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>24.15</v>
+        <v>23.65</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>79.625</v>
+        <v>77.125</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -22271,11 +22628,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>1.9906250000000001</v>
+        <v>1.9281250000000001</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.0456249999999998</v>
+        <v>1.1081249999999998</v>
       </c>
     </row>
   </sheetData>
@@ -22641,29 +22998,29 @@
         <v>15</v>
       </c>
       <c r="O9" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P9" s="11">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R9" s="11">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="S9" s="11">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="T9" s="11">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="U9" s="11">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>4.3</v>
+        <v>12.1</v>
       </c>
       <c r="W9" s="12">
         <v>3</v>
@@ -22674,11 +23031,11 @@
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>4.3</v>
+        <v>12.1</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0.70000000000000018</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22960,35 +23317,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>897</v>
+        <v>939</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>1025</v>
+        <v>1041</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>3471</v>
+        <v>3557</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>1496</v>
+        <v>1562</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>2745</v>
+        <v>2794</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>10993</v>
+        <v>11305</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -22997,11 +23354,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>274.82499999999999</v>
+        <v>282.625</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>-214.24999999999997</v>
+        <v>-222.04999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23048,35 +23405,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>22.425000000000001</v>
+        <v>23.475000000000001</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>25.625</v>
+        <v>26.024999999999999</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>86.775000000000006</v>
+        <v>88.924999999999997</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>30.574999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>37.4</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>68.625</v>
+        <v>69.849999999999994</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>274.82499999999999</v>
+        <v>282.625</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -23085,11 +23442,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>6.8706249999999995</v>
+        <v>7.0656249999999998</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>-5.3562499999999993</v>
+        <v>-5.5512499999999996</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795C3C20-925C-4ADE-B78B-2EEB2C7E903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334BD1C6-6A51-478F-911D-4C757E36BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="39">
   <si>
     <t>Booking</t>
   </si>
@@ -163,6 +163,15 @@
   </si>
   <si>
     <t>Shahid SB</t>
+  </si>
+  <si>
+    <t>Jabran</t>
+  </si>
+  <si>
+    <t>Jabran Iqbal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabran Iqbal </t>
   </si>
 </sst>
 </file>
@@ -3558,11 +3567,10 @@
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -3843,29 +3851,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>120</v>
+      </c>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>55</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>65</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9.5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>11</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>10.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>10.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -3906,29 +3930,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>22</v>
+      </c>
+      <c r="P9" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>6</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>56</v>
+      </c>
+      <c r="T9" s="11">
+        <v>50</v>
+      </c>
+      <c r="U9" s="11">
+        <v>60</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
+        <v>5</v>
+      </c>
+      <c r="W9" s="12">
+        <v>5</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>5.6</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>5.6</v>
+        <v>0.59999999999999964</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -3967,29 +4007,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>120</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>125</v>
+      </c>
+      <c r="T10" s="11">
+        <v>44</v>
+      </c>
+      <c r="U10" s="11">
+        <v>134</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>10.574999999999999</v>
+      </c>
+      <c r="W10" s="12">
+        <v>9</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>11.6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.574999999999999</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>11.6</v>
+        <v>1.0250000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -3998,7 +4054,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="11">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D11" s="11">
         <v>6</v>
@@ -4020,7 +4076,7 @@
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0.92500000000000004</v>
+        <v>1.9</v>
       </c>
       <c r="K11" s="12">
         <v>1</v>
@@ -4030,29 +4086,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>40</v>
+      </c>
+      <c r="P11" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>6</v>
+      </c>
+      <c r="R11" s="11">
+        <v>6</v>
+      </c>
+      <c r="S11" s="11">
+        <v>6</v>
+      </c>
+      <c r="T11" s="11">
+        <v>6</v>
+      </c>
+      <c r="U11" s="11">
+        <v>6</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>1.9</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0.92500000000000004</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0.92500000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -4093,29 +4165,45 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>4040</v>
+      </c>
+      <c r="P12" s="11">
+        <v>2200</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1960</v>
+      </c>
+      <c r="R12" s="11">
+        <v>1480</v>
+      </c>
+      <c r="S12" s="11">
+        <v>4560</v>
+      </c>
+      <c r="T12" s="11">
+        <v>3620</v>
+      </c>
+      <c r="U12" s="11">
+        <v>3520</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>534.5</v>
+      </c>
+      <c r="W12" s="12">
+        <v>7</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>97.5</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>534.5</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>97.5</v>
+        <v>-437</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4152,27 +4240,48 @@
         <v>2</v>
       </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="N13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O13" s="11">
+        <v>24</v>
+      </c>
+      <c r="P13" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>16</v>
+      </c>
+      <c r="R13" s="11">
+        <v>4</v>
+      </c>
+      <c r="S13" s="11">
+        <v>4</v>
+      </c>
+      <c r="T13" s="11">
+        <v>4</v>
+      </c>
+      <c r="U13" s="11">
+        <v>4</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>1.8</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -4180,7 +4289,7 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
@@ -4208,55 +4317,55 @@
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>5117</v>
+        <v>5156</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>4366</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2268</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2028</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1490</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3784</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3789</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>22531</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>127.925</v>
+        <v>128.9</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>563.27499999999998</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>127.925</v>
+        <v>-434.375</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4266,7 +4375,7 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>15.175000000000001</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
@@ -4294,7 +4403,7 @@
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>127.925</v>
+        <v>128.9</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -4303,48 +4412,48 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>109.15</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.25</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120.15</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>94.6</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>94.724999999999994</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>563.27499999999998</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>3.1981250000000001</v>
+        <v>3.2225000000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>14.081875</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>3.1981250000000001</v>
+        <v>-10.859375</v>
       </c>
     </row>
   </sheetData>
@@ -4367,7 +4476,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -4630,18 +4739,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>10</v>
+      </c>
+      <c r="D8" s="11">
+        <v>125</v>
+      </c>
+      <c r="E8" s="11">
+        <v>100</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>40</v>
+      </c>
+      <c r="H8" s="11">
+        <v>35</v>
+      </c>
+      <c r="I8" s="11">
+        <v>25</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>8.375</v>
+      </c>
+      <c r="K8" s="12">
+        <v>10</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -4661,7 +4786,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>8.375</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -4669,7 +4794,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>8.375</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -4685,7 +4810,7 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
       <c r="K9" s="12"/>
@@ -4724,18 +4849,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>172</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>110</v>
+      </c>
+      <c r="H10" s="11">
+        <v>60</v>
+      </c>
+      <c r="I10" s="11">
+        <v>60</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -4755,7 +4896,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -4763,7 +4904,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10.050000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -4771,18 +4912,28 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="C11" s="11">
+        <v>166</v>
+      </c>
+      <c r="D11" s="11">
+        <v>47</v>
+      </c>
+      <c r="E11" s="11">
+        <v>46</v>
+      </c>
+      <c r="F11" s="11">
+        <v>47</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>7.65</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -4802,7 +4953,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -4810,7 +4961,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -4818,18 +4969,35 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>40</v>
+      </c>
+      <c r="D12" s="11">
+        <v>40</v>
+      </c>
+      <c r="E12" s="11">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11">
+        <v>40</v>
+      </c>
+      <c r="G12" s="11">
+        <f>40+200</f>
+        <v>240</v>
+      </c>
+      <c r="H12" s="11">
+        <v>240</v>
+      </c>
+      <c r="I12" s="11">
+        <v>240</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="K12" s="12">
+        <v>2</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -4849,7 +5017,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -4857,23 +5025,46 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="B13" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="11">
+        <v>52</v>
+      </c>
+      <c r="D13" s="11">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11">
+        <v>4</v>
+      </c>
+      <c r="F13" s="11">
+        <v>4</v>
+      </c>
+      <c r="G13" s="11">
+        <v>19</v>
+      </c>
+      <c r="H13" s="11">
+        <v>14</v>
+      </c>
+      <c r="I13" s="11">
+        <v>19</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+      <c r="K13" s="12">
+        <v>3</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -4885,7 +5076,7 @@
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -4893,7 +5084,7 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -4901,35 +5092,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>2039</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -4969,7 +5160,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>50.975000000000001</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -4977,7 +5168,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>50.975000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4987,35 +5178,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.2749999999999999</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.225</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.7249999999999996</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50.975000000000001</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -5057,7 +5248,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>1.274375</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -5065,7 +5256,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.274375</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334BD1C6-6A51-478F-911D-4C757E36BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9393A2B-5A3A-4262-AAF5-5E1C8445688C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="39">
   <si>
     <t>Booking</t>
   </si>
@@ -4175,20 +4175,20 @@
         <v>1960</v>
       </c>
       <c r="R12" s="11">
-        <v>1480</v>
+        <v>1280</v>
       </c>
       <c r="S12" s="11">
-        <v>4560</v>
+        <v>4520</v>
       </c>
       <c r="T12" s="11">
-        <v>3620</v>
+        <v>3580</v>
       </c>
       <c r="U12" s="11">
-        <v>3520</v>
+        <v>3400</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>534.5</v>
+        <v>524.5</v>
       </c>
       <c r="W12" s="12">
         <v>7</v>
@@ -4199,11 +4199,11 @@
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>534.5</v>
+        <v>524.5</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>-437</v>
+        <v>-427</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4336,23 +4336,23 @@
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>4806</v>
+        <v>4766</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>3784</v>
+        <v>3744</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>3789</v>
+        <v>3669</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>22531</v>
+        <v>22131</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -4361,11 +4361,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>563.27499999999998</v>
+        <v>553.27499999999998</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>-434.375</v>
+        <v>-424.375</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4424,23 +4424,23 @@
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>37.25</v>
+        <v>32.25</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>120.15</v>
+        <v>119.15</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>94.6</v>
+        <v>93.6</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>94.724999999999994</v>
+        <v>91.724999999999994</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>563.27499999999998</v>
+        <v>553.27499999999998</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>14.081875</v>
+        <v>13.831875</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>-10.859375</v>
+        <v>-10.609375</v>
       </c>
     </row>
   </sheetData>
@@ -4772,29 +4772,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>10</v>
+      </c>
+      <c r="P8" s="11">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>25</v>
+      </c>
+      <c r="U8" s="11">
+        <v>15</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3.875</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>8.375</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>8.375</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -4802,46 +4818,78 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>60</v>
+      </c>
+      <c r="D9" s="11">
+        <v>20</v>
+      </c>
+      <c r="E9" s="11">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11">
+        <v>82</v>
+      </c>
+      <c r="H9" s="11">
+        <v>40</v>
+      </c>
+      <c r="I9" s="11">
+        <v>40</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>7.05</v>
+      </c>
+      <c r="K9" s="12">
+        <v>8</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>20</v>
+      </c>
+      <c r="P9" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>20</v>
+      </c>
+      <c r="R9" s="11">
+        <v>20</v>
+      </c>
+      <c r="S9" s="11">
+        <v>82</v>
+      </c>
+      <c r="T9" s="11">
+        <v>40</v>
+      </c>
+      <c r="U9" s="11">
+        <v>40</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
+        <v>6.05</v>
+      </c>
+      <c r="W9" s="12">
+        <v>8</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -4882,29 +4930,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>92</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>110</v>
+      </c>
+      <c r="T10" s="11">
+        <v>60</v>
+      </c>
+      <c r="U10" s="11">
+        <v>60</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>10.050000000000001</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>10.050000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -4939,29 +5003,39 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="O11" s="11">
+        <v>130</v>
+      </c>
+      <c r="P11" s="11">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>38</v>
+      </c>
+      <c r="R11" s="11">
+        <v>39</v>
+      </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>6.15</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>7.65</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>7.65</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -5003,29 +5077,45 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
+      <c r="P12" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>80</v>
+      </c>
+      <c r="R12" s="11">
+        <v>280</v>
+      </c>
+      <c r="S12" s="11">
+        <v>120</v>
+      </c>
+      <c r="T12" s="11">
+        <v>120</v>
+      </c>
+      <c r="U12" s="11">
+        <v>200</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -5065,26 +5155,45 @@
       <c r="N13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="O13" s="11">
+        <v>40</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11">
+        <v>15</v>
+      </c>
+      <c r="T13" s="11">
+        <v>10</v>
+      </c>
+      <c r="U13" s="11">
+        <v>15</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>2.9</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>2.9</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -5092,83 +5201,83 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>2039</v>
+        <v>2321</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1965</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>50.975000000000001</v>
+        <v>58.024999999999999</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>49.125</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>50.975000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5178,35 +5287,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>2.2749999999999999</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>10.225</v>
+        <v>12.275</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>8.7249999999999996</v>
+        <v>9.7249999999999996</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>50.975000000000001</v>
+        <v>58.024999999999999</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -5215,48 +5324,48 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.1750000000000007</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>49.125</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>1.274375</v>
+        <v>1.4506250000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>1.2281249999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.274375</v>
+        <v>0.2225</v>
       </c>
     </row>
   </sheetData>
@@ -6264,17 +6373,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>80</v>
+      </c>
+      <c r="E8" s="11">
+        <v>80</v>
+      </c>
+      <c r="F8" s="11">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11">
+        <v>80</v>
+      </c>
+      <c r="H8" s="11">
+        <v>80</v>
+      </c>
+      <c r="I8" s="11">
+        <v>40</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K8" s="12">
+        <v>10</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -6294,7 +6417,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -6302,7 +6425,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -6310,18 +6433,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>72</v>
+      </c>
+      <c r="D9" s="11">
+        <v>10</v>
+      </c>
+      <c r="E9" s="11">
+        <v>27</v>
+      </c>
+      <c r="F9" s="11">
+        <v>27</v>
+      </c>
+      <c r="G9" s="11">
+        <v>107</v>
+      </c>
+      <c r="H9" s="11">
+        <v>107</v>
+      </c>
+      <c r="I9" s="11">
+        <v>207</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>13.925000000000001</v>
+      </c>
+      <c r="K9" s="12">
+        <v>13</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -6341,7 +6480,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>13.925000000000001</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -6349,7 +6488,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>13.925000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -6404,18 +6543,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>112</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>12</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>7</v>
+      </c>
+      <c r="H11" s="11">
+        <v>7</v>
+      </c>
+      <c r="I11" s="11">
+        <v>6</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>3</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -6435,7 +6590,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -6443,30 +6598,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>38</v>
+      </c>
+      <c r="C12" s="11">
+        <v>52</v>
+      </c>
+      <c r="D12" s="11">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>103</v>
+      </c>
+      <c r="H12" s="11">
+        <v>73</v>
+      </c>
+      <c r="I12" s="11">
+        <v>88</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>8.15</v>
+      </c>
+      <c r="K12" s="12">
+        <v>8</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -6482,7 +6653,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -6490,12 +6661,14 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -6506,7 +6679,9 @@
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -6534,35 +6709,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>1427</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -6602,7 +6777,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>35.675000000000004</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -6610,7 +6785,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>35.675000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6620,35 +6795,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.675</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.4249999999999998</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.5250000000000004</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>35.674999999999997</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -6690,7 +6865,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>0.89187500000000008</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -6698,7 +6873,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>0.89187500000000008</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9393A2B-5A3A-4262-AAF5-5E1C8445688C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FFFF88-8542-4FA7-8B95-134E2E11C634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="12" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -4178,17 +4178,20 @@
         <v>1280</v>
       </c>
       <c r="S12" s="11">
-        <v>4520</v>
+        <f>4520+880</f>
+        <v>5400</v>
       </c>
       <c r="T12" s="11">
-        <v>3580</v>
+        <f>3580+640</f>
+        <v>4220</v>
       </c>
       <c r="U12" s="11">
-        <v>3400</v>
+        <f>3400+880+2000</f>
+        <v>6280</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>524.5</v>
+        <v>634.5</v>
       </c>
       <c r="W12" s="12">
         <v>7</v>
@@ -4199,11 +4202,11 @@
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>524.5</v>
+        <v>634.5</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>-427</v>
+        <v>-537</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4340,19 +4343,19 @@
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>4766</v>
+        <v>5646</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>3744</v>
+        <v>4384</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>3669</v>
+        <v>6549</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>22131</v>
+        <v>26531</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -4361,11 +4364,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>553.27499999999998</v>
+        <v>663.27499999999998</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>-424.375</v>
+        <v>-534.375</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4428,19 +4431,19 @@
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>119.15</v>
+        <v>141.15</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>93.6</v>
+        <v>109.6</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>91.724999999999994</v>
+        <v>163.72499999999999</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>553.27499999999998</v>
+        <v>663.27499999999998</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -4449,11 +4452,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>13.831875</v>
+        <v>16.581875</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>-10.609375</v>
+        <v>-13.359375</v>
       </c>
     </row>
   </sheetData>
@@ -5651,13 +5654,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -5668,13 +5671,13 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
@@ -5698,13 +5701,13 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -5715,13 +5718,13 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
@@ -5745,13 +5748,13 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5762,13 +5765,13 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5792,13 +5795,13 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5809,13 +5812,13 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5839,13 +5842,13 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5856,13 +5859,13 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5884,24 +5887,24 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
       <c r="V13" s="15"/>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
@@ -6372,7 +6375,9 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
+      <c r="C8" s="11">
+        <v>280</v>
+      </c>
       <c r="D8" s="11">
         <v>80</v>
       </c>
@@ -6380,20 +6385,20 @@
         <v>80</v>
       </c>
       <c r="F8" s="11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="H8" s="11">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="I8" s="11">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" s="12">
         <v>10</v>
@@ -6417,7 +6422,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -6425,7 +6430,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -6455,7 +6460,7 @@
         <v>207</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>13.925000000000001</v>
       </c>
       <c r="K9" s="12">
@@ -6496,18 +6501,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>132</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>117</v>
+      </c>
+      <c r="H10" s="11">
+        <v>135</v>
+      </c>
+      <c r="I10" s="11">
+        <v>152</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>13.4</v>
+      </c>
+      <c r="K10" s="12">
+        <v>10</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -6527,7 +6548,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -6535,7 +6556,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -6669,15 +6690,41 @@
       <c r="B13" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="C13" s="11">
+        <f>80+40</f>
+        <v>120</v>
+      </c>
+      <c r="D13" s="11">
+        <f>120+120+40</f>
+        <v>280</v>
+      </c>
+      <c r="E13" s="11">
+        <f>120+80+20</f>
+        <v>220</v>
+      </c>
+      <c r="F13" s="11">
+        <f>120+40+20</f>
+        <v>180</v>
+      </c>
+      <c r="G13" s="11">
+        <f>120+440+20</f>
+        <v>580</v>
+      </c>
+      <c r="H13" s="11">
+        <f>120+200+40</f>
+        <v>360</v>
+      </c>
+      <c r="I13" s="11">
+        <f>120+80+20</f>
+        <v>220</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="K13" s="18">
+        <v>3</v>
+      </c>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
         <v>18</v>
@@ -6693,7 +6740,7 @@
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -6701,7 +6748,7 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -6709,35 +6756,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>236</v>
+        <v>768</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>119</v>
+        <v>339</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>67</v>
+        <v>207</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>297</v>
+        <v>929</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>267</v>
+        <v>692</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>341</v>
+        <v>688</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>1427</v>
+        <v>4003</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -6777,7 +6824,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>35.675000000000004</v>
+        <v>100.075</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -6785,7 +6832,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>35.675000000000004</v>
+        <v>100.075</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6795,35 +6842,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>5.9</v>
+        <v>19.2</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>2.9750000000000001</v>
+        <v>8.4749999999999996</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>1.675</v>
+        <v>5.1749999999999998</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>7.4249999999999998</v>
+        <v>23.225000000000001</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>6.6749999999999998</v>
+        <v>17.3</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>8.5250000000000004</v>
+        <v>17.2</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>35.674999999999997</v>
+        <v>100.075</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -6865,7 +6912,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0.89187500000000008</v>
+        <v>2.5018750000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -6873,7 +6920,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0.89187500000000008</v>
+        <v>2.5018750000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FFFF88-8542-4FA7-8B95-134E2E11C634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F142C1C5-17E3-4C37-B444-98188E1B07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="14" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="40">
   <si>
     <t>Booking</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jabran Iqbal </t>
+  </si>
+  <si>
+    <t>Furqan</t>
   </si>
 </sst>
 </file>
@@ -6471,29 +6474,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>40</v>
+      </c>
+      <c r="P9" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>27</v>
+      </c>
+      <c r="R9" s="11">
+        <v>27</v>
+      </c>
+      <c r="S9" s="11">
+        <v>87</v>
+      </c>
+      <c r="T9" s="11">
+        <v>87</v>
+      </c>
+      <c r="U9" s="11">
+        <v>167</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>11.05</v>
+      </c>
+      <c r="W9" s="12">
+        <v>5</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>13.925000000000001</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>11.05</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>13.925000000000001</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -6597,29 +6616,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>112</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>12</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>7</v>
+      </c>
+      <c r="T11" s="11">
+        <v>7</v>
+      </c>
+      <c r="U11" s="11">
+        <v>6</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>3</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>3.6</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -6660,29 +6695,45 @@
       <c r="N12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>70</v>
+      </c>
+      <c r="T12" s="11">
+        <v>60</v>
+      </c>
+      <c r="U12" s="11">
+        <v>70</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>8.15</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>8.15</v>
+        <v>2.1500000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -6791,35 +6842,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -6828,11 +6879,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>100.075</v>
+        <v>79.424999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6879,35 +6930,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.0750000000000002</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -6916,11 +6967,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.51624999999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>2.5018750000000001</v>
+        <v>1.985625</v>
       </c>
     </row>
   </sheetData>
@@ -7206,13 +7257,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -7223,13 +7274,13 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
@@ -7253,13 +7304,13 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -7270,13 +7321,13 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
@@ -7300,13 +7351,13 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7317,13 +7368,13 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7347,13 +7398,13 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7364,13 +7415,13 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7394,13 +7445,13 @@
       <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7411,13 +7462,13 @@
       <c r="N12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7439,24 +7490,24 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
       <c r="V13" s="15"/>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
@@ -7927,18 +7978,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>440</v>
+      </c>
+      <c r="D8" s="11">
+        <v>200</v>
+      </c>
+      <c r="E8" s="11">
+        <v>140</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>180</v>
+      </c>
+      <c r="H8" s="11">
+        <v>130</v>
+      </c>
+      <c r="I8" s="11">
+        <v>175</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>31.625</v>
+      </c>
+      <c r="K8" s="12">
+        <v>15</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -7958,7 +8025,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>31.625</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -7966,7 +8033,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>31.625</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -7974,18 +8041,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>32</v>
+      </c>
+      <c r="D9" s="11">
+        <v>55</v>
+      </c>
+      <c r="E9" s="11">
+        <v>36</v>
+      </c>
+      <c r="F9" s="11">
+        <v>41</v>
+      </c>
+      <c r="G9" s="11">
+        <v>55</v>
+      </c>
+      <c r="H9" s="11">
+        <v>45</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>8.1</v>
+      </c>
+      <c r="K9" s="12">
+        <v>9</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -7999,13 +8082,13 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -8013,7 +8096,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8021,18 +8104,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>100</v>
+      </c>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>77</v>
+      </c>
+      <c r="H10" s="11">
+        <v>125</v>
+      </c>
+      <c r="I10" s="11">
+        <v>126</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>11.2</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -8052,7 +8151,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -8060,7 +8159,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -8068,18 +8167,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>120</v>
+      </c>
+      <c r="D11" s="11">
+        <v>40</v>
+      </c>
+      <c r="E11" s="11">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11">
+        <v>40</v>
+      </c>
+      <c r="G11" s="11">
+        <v>55</v>
+      </c>
+      <c r="H11" s="11">
+        <v>50</v>
+      </c>
+      <c r="I11" s="11">
+        <v>55</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K11" s="12">
+        <v>4</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -8099,7 +8214,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -8107,13 +8222,13 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -8130,7 +8245,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -8159,18 +8274,41 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="B13" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="11">
+        <v>36</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <v>12</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>15</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>1.575</v>
+      </c>
+      <c r="K13" s="18">
+        <v>5</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -8178,11 +8316,14 @@
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -8190,7 +8331,7 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -8198,35 +8339,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -8266,7 +8407,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -8274,7 +8415,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8284,35 +8425,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -8354,7 +8495,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -8362,7 +8503,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.5625</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F142C1C5-17E3-4C37-B444-98188E1B07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05A1D14-9CAE-4473-BF2D-E15C9DA93DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="14" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -8011,29 +8011,46 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <f>160+40</f>
+        <v>200</v>
+      </c>
+      <c r="P8" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>120</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>170</v>
+      </c>
+      <c r="T8" s="11">
+        <v>120</v>
+      </c>
+      <c r="U8" s="11">
+        <v>160</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>22.25</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>31.625</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>31.625</v>
+        <v>9.375</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -8074,29 +8091,52 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <f>32+40</f>
+        <v>72</v>
+      </c>
+      <c r="P9" s="11">
+        <f>35+7</f>
+        <v>42</v>
+      </c>
+      <c r="Q9" s="11">
+        <f>36+27</f>
+        <v>63</v>
+      </c>
+      <c r="R9" s="11">
+        <f>21+27</f>
+        <v>48</v>
+      </c>
+      <c r="S9" s="11">
+        <f>30+87</f>
+        <v>117</v>
+      </c>
+      <c r="T9" s="11">
+        <f>25+87</f>
+        <v>112</v>
+      </c>
+      <c r="U9" s="11">
+        <f>25+167</f>
+        <v>192</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="W9" s="12">
+        <v>13</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>8.1</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>8.1</v>
+        <v>-8.0499999999999989</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8137,29 +8177,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>40</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>55</v>
+      </c>
+      <c r="T10" s="11">
+        <v>95</v>
+      </c>
+      <c r="U10" s="11">
+        <v>90</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>11.2</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>11.2</v>
+        <v>4.1999999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -8200,29 +8256,50 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <f>120+112</f>
+        <v>232</v>
+      </c>
+      <c r="P11" s="11">
+        <f>40+12</f>
+        <v>52</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>40</v>
+      </c>
+      <c r="R11" s="11">
+        <v>40</v>
+      </c>
+      <c r="S11" s="11">
+        <f>55+7</f>
+        <v>62</v>
+      </c>
+      <c r="T11" s="11">
+        <f>50+7</f>
+        <v>57</v>
+      </c>
+      <c r="U11" s="11">
+        <f>55+6</f>
+        <v>61</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>13.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>12</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>-3.5999999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -8247,29 +8324,45 @@
       <c r="N12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>70</v>
+      </c>
+      <c r="T12" s="11">
+        <v>60</v>
+      </c>
+      <c r="U12" s="11">
+        <v>70</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -8309,29 +8402,45 @@
       <c r="N13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="11">
+        <v>12</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>12</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11">
+        <v>15</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="18"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="W13" s="12">
+        <v>3</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>1.575</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>1.575</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -8374,35 +8483,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>2639</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -8411,11 +8520,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>65.974999999999994</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>62.5</v>
+        <v>-3.4749999999999992</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8462,35 +8571,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.225</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.324999999999999</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>65.974999999999994</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -8499,11 +8608,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>1.6493749999999998</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.5625</v>
+        <v>-8.687499999999998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8789,18 +8898,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>229</v>
+      </c>
+      <c r="D8" s="11">
+        <v>8</v>
+      </c>
+      <c r="E8" s="11">
+        <v>43</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>75</v>
+      </c>
+      <c r="H8" s="11">
+        <v>53</v>
+      </c>
+      <c r="I8" s="11">
+        <v>82</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>12.25</v>
+      </c>
+      <c r="K8" s="12">
+        <v>16</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -8820,7 +8945,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -8828,7 +8953,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -8836,18 +8961,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>92</v>
+      </c>
+      <c r="D9" s="11">
+        <v>82</v>
+      </c>
+      <c r="E9" s="11">
+        <v>70</v>
+      </c>
+      <c r="F9" s="11">
+        <v>62</v>
+      </c>
+      <c r="G9" s="11">
+        <v>42</v>
+      </c>
+      <c r="H9" s="11">
+        <v>32</v>
+      </c>
+      <c r="I9" s="11">
+        <v>48</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10.7</v>
+      </c>
+      <c r="K9" s="12">
+        <v>10</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -8867,7 +9008,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -8875,7 +9016,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8883,18 +9024,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>190</v>
+      </c>
+      <c r="D10" s="11">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>147</v>
+      </c>
+      <c r="H10" s="11">
+        <v>156</v>
+      </c>
+      <c r="I10" s="11">
+        <v>153</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>17.149999999999999</v>
+      </c>
+      <c r="K10" s="12">
+        <v>10</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -8914,7 +9071,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -8922,7 +9079,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17.149999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -8930,18 +9087,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>5</v>
+      </c>
+      <c r="D11" s="11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="11">
+        <v>6</v>
+      </c>
+      <c r="F11" s="11">
+        <v>6</v>
+      </c>
+      <c r="G11" s="11">
+        <v>6</v>
+      </c>
+      <c r="H11" s="11">
+        <v>6</v>
+      </c>
+      <c r="I11" s="11">
+        <v>6</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="K11" s="12">
+        <v>2</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -8961,7 +9134,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -8969,7 +9142,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9060,35 +9233,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>1645</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -9128,7 +9301,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>41.124999999999993</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -9136,7 +9309,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>41.124999999999993</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9146,35 +9319,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.1749999999999998</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>41.125</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -9216,7 +9389,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>1.0281249999999997</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -9224,7 +9397,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.0281249999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05A1D14-9CAE-4473-BF2D-E15C9DA93DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409A9C8E-4F7D-4227-892B-7C73506D3DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="19" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="42">
   <si>
     <t>Booking</t>
   </si>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>Furqan</t>
+  </si>
+  <si>
+    <t>Jabar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasan </t>
   </si>
 </sst>
 </file>
@@ -8931,29 +8937,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>189</v>
+      </c>
+      <c r="P8" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>43</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>60</v>
+      </c>
+      <c r="T8" s="11">
+        <v>43</v>
+      </c>
+      <c r="U8" s="11">
+        <v>67</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>10.25</v>
+      </c>
+      <c r="W8" s="12">
+        <v>15</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>12.25</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>12.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -8994,29 +9016,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>92</v>
+      </c>
+      <c r="P9" s="11">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>70</v>
+      </c>
+      <c r="R9" s="11">
+        <v>62</v>
+      </c>
+      <c r="S9" s="11">
+        <v>42</v>
+      </c>
+      <c r="T9" s="11">
+        <v>32</v>
+      </c>
+      <c r="U9" s="11">
+        <v>48</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>10.7</v>
+      </c>
+      <c r="W9" s="12">
+        <v>10</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>10.7</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9057,29 +9095,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>110</v>
+      </c>
+      <c r="P10" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>20</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>107</v>
+      </c>
+      <c r="T10" s="11">
+        <v>110</v>
+      </c>
+      <c r="U10" s="11">
+        <v>119</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>12.15</v>
+      </c>
+      <c r="W10" s="12">
+        <v>9</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>17.149999999999999</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.15</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>17.149999999999999</v>
+        <v>4.9999999999999982</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9168,15 +9222,27 @@
         <v>18</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>280</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>288</v>
+      </c>
+      <c r="R12" s="11">
+        <v>680</v>
+      </c>
+      <c r="S12" s="11">
+        <v>440</v>
+      </c>
+      <c r="T12" s="11">
+        <v>599</v>
+      </c>
+      <c r="U12" s="11">
+        <v>600</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72.174999999999997</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
@@ -9185,11 +9251,11 @@
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>72.174999999999997</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-72.174999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -9268,35 +9334,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>4211</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -9305,11 +9371,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>105.27500000000001</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>41.124999999999993</v>
+        <v>-64.150000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9356,35 +9422,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>9.7750000000000004</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.525</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18.55</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.225000000000001</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20.85</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>105.27500000000001</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -9393,11 +9459,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>2.631875</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.0281249999999997</v>
+        <v>-1.6037500000000002</v>
       </c>
     </row>
   </sheetData>
@@ -9416,11 +9482,11 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FED4E2C-B3C5-473E-8709-91E86C4798CE}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -9428,7 +9494,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -9683,18 +9749,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>234</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>74</v>
+      </c>
+      <c r="H8" s="11">
+        <v>39</v>
+      </c>
+      <c r="I8" s="11">
+        <v>169</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>12.9</v>
+      </c>
+      <c r="K8" s="12">
+        <v>15</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -9714,7 +9796,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -9722,7 +9804,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9730,18 +9812,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>40</v>
+      </c>
+      <c r="G9" s="11">
+        <v>53</v>
+      </c>
+      <c r="H9" s="11">
+        <v>52</v>
+      </c>
+      <c r="I9" s="11">
+        <v>55</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K9" s="12">
+        <v>11</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -9761,7 +9859,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -9769,7 +9867,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9777,18 +9875,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>300</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>100</v>
+      </c>
+      <c r="H10" s="11">
+        <v>94</v>
+      </c>
+      <c r="I10" s="11">
+        <v>92</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>14.65</v>
+      </c>
+      <c r="K10" s="12">
+        <v>11</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -9808,7 +9922,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -9816,7 +9930,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9824,18 +9938,34 @@
       <c r="B11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>34</v>
+      </c>
+      <c r="D11" s="11">
+        <v>43</v>
+      </c>
+      <c r="E11" s="11">
+        <v>43</v>
+      </c>
+      <c r="F11" s="11">
+        <v>43</v>
+      </c>
+      <c r="G11" s="11">
+        <v>38</v>
+      </c>
+      <c r="H11" s="11">
+        <v>35</v>
+      </c>
+      <c r="I11" s="11">
+        <v>30</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6.65</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -9855,7 +9985,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -9863,7 +9993,7 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9872,21 +10002,35 @@
         <v>17</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>600</v>
+      </c>
+      <c r="E12" s="11">
+        <v>600</v>
+      </c>
+      <c r="F12" s="11">
+        <v>600</v>
+      </c>
+      <c r="G12" s="11">
+        <v>600</v>
+      </c>
+      <c r="H12" s="11">
+        <v>600</v>
+      </c>
+      <c r="I12" s="11">
+        <v>600</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>90</v>
+      </c>
+      <c r="K12" s="12">
+        <v>1</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -9902,7 +10046,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -9910,7 +10054,7 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -9954,35 +10098,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>946</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>5288</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -10022,7 +10166,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -10030,7 +10174,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>132.19999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10040,35 +10184,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>16.074999999999999</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.074999999999999</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.074999999999999</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21.625</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -10110,7 +10254,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>3.3049999999999997</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -10118,7 +10262,13 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>3.3049999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J23">
+        <f>15*40</f>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -10864,7 +11014,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE02268-B5C0-4F7D-B124-8932172B8A1F}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -11131,18 +11281,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>222</v>
+      </c>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>114</v>
+      </c>
+      <c r="H8" s="11">
+        <v>52</v>
+      </c>
+      <c r="I8" s="11">
+        <v>84</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>12.8</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -11162,7 +11328,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -11170,7 +11336,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -11178,18 +11344,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>128</v>
+      </c>
+      <c r="D9" s="11">
+        <v>73</v>
+      </c>
+      <c r="E9" s="11">
+        <v>92</v>
+      </c>
+      <c r="F9" s="11">
+        <v>32</v>
+      </c>
+      <c r="G9" s="11">
+        <v>82</v>
+      </c>
+      <c r="H9" s="11">
+        <v>26</v>
+      </c>
+      <c r="I9" s="11">
+        <v>26</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J14" si="0">SUM(C9:I9)/40</f>
+        <v>11.475</v>
+      </c>
+      <c r="K9" s="12">
+        <v>10</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -11203,13 +11385,13 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V14" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>11.475</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -11217,7 +11399,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>11.475</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -11225,18 +11407,28 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11">
+        <v>192</v>
+      </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11">
+        <v>100</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>60</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -11256,7 +11448,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -11264,15 +11456,17 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="C11" s="11">
+        <v>24</v>
+      </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -11281,13 +11475,15 @@
       <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>2</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -11303,7 +11499,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -11311,30 +11507,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>147</v>
+      </c>
+      <c r="D12" s="11">
+        <v>15</v>
+      </c>
+      <c r="E12" s="11">
+        <v>54</v>
+      </c>
+      <c r="F12" s="11">
+        <v>15</v>
+      </c>
+      <c r="G12" s="11">
+        <v>31</v>
+      </c>
+      <c r="H12" s="11">
+        <v>10</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.8</v>
+      </c>
+      <c r="K12" s="12">
+        <v>10</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -11350,7 +11562,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -11358,23 +11570,46 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="B13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="11">
+        <v>40</v>
+      </c>
+      <c r="D13" s="11">
+        <v>10</v>
+      </c>
+      <c r="E13" s="11">
+        <v>20</v>
+      </c>
+      <c r="F13" s="11">
+        <v>40</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13" s="11">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>2.8250000000000002</v>
+      </c>
+      <c r="K13" s="18">
+        <v>3</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -11382,11 +11617,14 @@
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.8250000000000002</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -11394,179 +11632,241 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.8250000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25">
-        <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <f>SUM(C14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="25">
-        <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="28">
-        <f>SUM(O14:U14)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="31"/>
-      <c r="Y14" s="36">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="11">
+        <v>80</v>
+      </c>
+      <c r="D14" s="11">
+        <v>320</v>
+      </c>
+      <c r="E14" s="11">
+        <v>160</v>
+      </c>
+      <c r="F14" s="11">
+        <v>600</v>
+      </c>
+      <c r="G14" s="11">
+        <v>360</v>
+      </c>
+      <c r="H14" s="11">
+        <v>160</v>
+      </c>
+      <c r="I14" s="11">
+        <v>760</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="K14" s="18">
+        <v>6</v>
+      </c>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="18"/>
+      <c r="Y14" s="39">
+        <f t="shared" ref="Y14" si="5">J14</f>
+        <v>61</v>
+      </c>
+      <c r="Z14" s="40">
+        <f t="shared" ref="Z14" si="6">V14</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="41">
+        <f t="shared" ref="AA14" si="7">Y14-Z14</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="25">
+        <f>SUM(C8:C14)</f>
+        <v>833</v>
+      </c>
+      <c r="D15" s="25">
+        <f>SUM(D8:D14)</f>
+        <v>438</v>
+      </c>
+      <c r="E15" s="25">
+        <f>SUM(E8:E14)</f>
+        <v>346</v>
+      </c>
+      <c r="F15" s="25">
+        <f>SUM(F8:F14)</f>
+        <v>687</v>
+      </c>
+      <c r="G15" s="25">
+        <f>SUM(G8:G14)</f>
+        <v>688</v>
+      </c>
+      <c r="H15" s="25">
+        <f>SUM(H8:H14)</f>
+        <v>249</v>
+      </c>
+      <c r="I15" s="25">
+        <f>SUM(I8:I14)</f>
+        <v>931</v>
+      </c>
+      <c r="J15" s="28">
+        <f>SUM(C15:I15)</f>
+        <v>4172</v>
+      </c>
+      <c r="K15" s="31"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="25">
+        <f t="shared" ref="O15:U15" si="8">SUM(O8:O13)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="28">
+        <f>SUM(O15:U15)</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="31"/>
+      <c r="Y15" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="37">
+        <v>43.300000000000004</v>
+      </c>
+      <c r="Z15" s="37">
         <f>SUM(Z8:Z13)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="38">
+      <c r="AA15" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+        <v>43.300000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="21">
-        <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="23"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="20" t="s">
+      <c r="C16" s="21">
+        <f t="shared" ref="C16:J16" si="9">C15/40</f>
+        <v>20.824999999999999</v>
+      </c>
+      <c r="D16" s="21">
+        <f t="shared" si="9"/>
+        <v>10.95</v>
+      </c>
+      <c r="E16" s="21">
+        <f t="shared" si="9"/>
+        <v>8.65</v>
+      </c>
+      <c r="F16" s="21">
+        <f t="shared" si="9"/>
+        <v>17.175000000000001</v>
+      </c>
+      <c r="G16" s="21">
+        <f t="shared" si="9"/>
+        <v>17.2</v>
+      </c>
+      <c r="H16" s="21">
+        <f t="shared" si="9"/>
+        <v>6.2249999999999996</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="9"/>
+        <v>23.274999999999999</v>
+      </c>
+      <c r="J16" s="22">
+        <f t="shared" si="9"/>
+        <v>104.3</v>
+      </c>
+      <c r="K16" s="23"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="O15" s="21">
-        <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="23"/>
-      <c r="Y15" s="42">
-        <f>Y14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="43">
-        <f>Z14/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44">
-        <f>AA14/40</f>
-        <v>0</v>
+      <c r="O16" s="21">
+        <f t="shared" ref="O16:V16" si="10">O15/40</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="23"/>
+      <c r="Y16" s="42">
+        <f>Y15/40</f>
+        <v>1.0825</v>
+      </c>
+      <c r="Z16" s="43">
+        <f>Z15/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="44">
+        <f>AA15/40</f>
+        <v>1.0825</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409A9C8E-4F7D-4227-892B-7C73506D3DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E8B55-6C12-4428-8451-5BA6BC975965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="19" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="44">
   <si>
     <t>Booking</t>
   </si>
@@ -182,12 +182,18 @@
   <si>
     <t xml:space="preserve">Hasan </t>
   </si>
+  <si>
+    <t xml:space="preserve">Jabbar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furqan </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +302,14 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -496,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -656,6 +670,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,103 +1058,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="75" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="75"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="75"/>
-      <c r="AA4" s="75"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1154,16 +1171,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1171,16 +1188,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1851,103 +1868,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1964,16 +1981,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1981,16 +1998,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2710,103 +2727,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2823,16 +2840,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2840,16 +2857,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3608,103 +3625,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3721,16 +3738,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3738,16 +3755,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4532,103 +4549,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4645,16 +4662,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4662,16 +4679,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5444,103 +5461,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5557,16 +5574,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5574,16 +5591,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6165,103 +6182,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6278,16 +6295,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6295,16 +6312,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7044,103 +7061,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7157,16 +7174,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7174,16 +7191,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7765,103 +7782,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7878,16 +7895,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7895,16 +7912,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8685,103 +8702,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8798,16 +8815,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8815,16 +8832,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9530,103 +9547,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9643,16 +9660,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9660,16 +9677,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9782,29 +9799,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>254</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>59</v>
+      </c>
+      <c r="T8" s="11">
+        <v>24</v>
+      </c>
+      <c r="U8" s="11">
+        <v>79</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>10.9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>12.9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>12.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9845,29 +9878,48 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <f>53+80</f>
+        <v>133</v>
+      </c>
+      <c r="T9" s="11">
+        <f>52+80</f>
+        <v>132</v>
+      </c>
+      <c r="U9" s="11">
+        <f>55+80</f>
+        <v>135</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="W9" s="12">
+        <v>11</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>8</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9908,29 +9960,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>220</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>73</v>
+      </c>
+      <c r="T10" s="11">
+        <v>67</v>
+      </c>
+      <c r="U10" s="11">
+        <v>66</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>10.65</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>14.65</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>14.65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9971,29 +10039,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>33</v>
+      </c>
+      <c r="P11" s="11">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>42</v>
+      </c>
+      <c r="R11" s="11">
+        <v>42</v>
+      </c>
+      <c r="S11" s="11">
+        <v>40</v>
+      </c>
+      <c r="T11" s="11">
+        <v>37</v>
+      </c>
+      <c r="U11" s="11">
+        <v>32</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>6.7</v>
+      </c>
+      <c r="W11" s="12">
+        <v>9</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>6.65</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>6.65</v>
+        <v>-4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -10133,35 +10217,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1690</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -10170,11 +10254,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>42.25</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>132.19999999999999</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10221,35 +10305,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>14.675000000000001</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>42.25</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -10258,11 +10342,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>1.0562499999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>3.3049999999999997</v>
+        <v>2.2487500000000002</v>
       </c>
     </row>
     <row r="23" spans="10:10" x14ac:dyDescent="0.35">
@@ -10325,10 +10409,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="79" t="s">
+      <c r="L1" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="79"/>
+      <c r="M1" s="80"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -10340,103 +10424,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10453,16 +10537,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10470,16 +10554,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11027,13 +11111,13 @@
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.26953125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -11062,103 +11146,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11175,16 +11259,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11192,16 +11276,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11314,29 +11398,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>98</v>
+      </c>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>89</v>
+      </c>
+      <c r="T8" s="11">
+        <v>32</v>
+      </c>
+      <c r="U8" s="11">
+        <v>59</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>7.95</v>
+      </c>
+      <c r="W8" s="12">
+        <v>6</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>12.8</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>12.8</v>
+        <v>4.8500000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -11377,29 +11477,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>72</v>
+      </c>
+      <c r="P9" s="11">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>62</v>
+      </c>
+      <c r="R9" s="11">
+        <v>32</v>
+      </c>
+      <c r="S9" s="11">
+        <v>52</v>
+      </c>
+      <c r="T9" s="11">
+        <v>36</v>
+      </c>
+      <c r="U9" s="11">
+        <v>16</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V14" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>7.8</v>
+      </c>
+      <c r="W9" s="12">
+        <v>7</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>11.475</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>11.475</v>
+        <v>3.6749999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -11434,29 +11550,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>192</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>100</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <v>60</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>8.8000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -11485,7 +11617,9 @@
       <c r="N11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="11">
+        <v>24</v>
+      </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -11494,7 +11628,7 @@
       <c r="U11" s="11"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
@@ -11503,11 +11637,11 @@
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -11673,15 +11807,27 @@
         <v>17</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="P14" s="11">
+        <v>160</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>120</v>
+      </c>
+      <c r="R14" s="11">
+        <v>840</v>
+      </c>
+      <c r="S14" s="11">
+        <v>319</v>
+      </c>
+      <c r="T14" s="11">
+        <v>160</v>
+      </c>
+      <c r="U14" s="11">
+        <v>680</v>
+      </c>
       <c r="V14" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>56.975000000000001</v>
       </c>
       <c r="W14" s="18"/>
       <c r="Y14" s="39">
@@ -11690,42 +11836,42 @@
       </c>
       <c r="Z14" s="40">
         <f t="shared" ref="Z14" si="6">V14</f>
-        <v>0</v>
+        <v>56.975000000000001</v>
       </c>
       <c r="AA14" s="41">
         <f t="shared" ref="AA14" si="7">Y14-Z14</f>
-        <v>61</v>
+        <v>4.0249999999999986</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="7"/>
       <c r="C15" s="25">
-        <f>SUM(C8:C14)</f>
+        <f t="shared" ref="C15:I15" si="8">SUM(C8:C14)</f>
         <v>833</v>
       </c>
       <c r="D15" s="25">
-        <f>SUM(D8:D14)</f>
+        <f t="shared" si="8"/>
         <v>438</v>
       </c>
       <c r="E15" s="25">
-        <f>SUM(E8:E14)</f>
+        <f t="shared" si="8"/>
         <v>346</v>
       </c>
       <c r="F15" s="25">
-        <f>SUM(F8:F14)</f>
+        <f t="shared" si="8"/>
         <v>687</v>
       </c>
       <c r="G15" s="25">
-        <f>SUM(G8:G14)</f>
+        <f t="shared" si="8"/>
         <v>688</v>
       </c>
       <c r="H15" s="25">
-        <f>SUM(H8:H14)</f>
+        <f t="shared" si="8"/>
         <v>249</v>
       </c>
       <c r="I15" s="25">
-        <f>SUM(I8:I14)</f>
+        <f t="shared" si="8"/>
         <v>931</v>
       </c>
       <c r="J15" s="28">
@@ -11735,37 +11881,37 @@
       <c r="K15" s="31"/>
       <c r="M15" s="1"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="25">
-        <f t="shared" ref="O15:U15" si="8">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
+      <c r="O15" s="75">
+        <f>SUM(O8:O14)</f>
+        <v>386</v>
+      </c>
+      <c r="P15" s="75">
+        <f t="shared" ref="P15:U15" si="9">SUM(P8:P14)</f>
+        <v>222</v>
+      </c>
+      <c r="Q15" s="75">
+        <f t="shared" si="9"/>
+        <v>202</v>
+      </c>
+      <c r="R15" s="75">
+        <f t="shared" si="9"/>
+        <v>872</v>
+      </c>
+      <c r="S15" s="75">
+        <f t="shared" si="9"/>
+        <v>560</v>
+      </c>
+      <c r="T15" s="75">
+        <f t="shared" si="9"/>
+        <v>228</v>
+      </c>
+      <c r="U15" s="75">
+        <f t="shared" si="9"/>
+        <v>815</v>
       </c>
       <c r="V15" s="28">
         <f>SUM(O15:U15)</f>
-        <v>0</v>
+        <v>3285</v>
       </c>
       <c r="W15" s="31"/>
       <c r="Y15" s="36">
@@ -11774,11 +11920,11 @@
       </c>
       <c r="Z15" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>25.150000000000002</v>
       </c>
       <c r="AA15" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>43.300000000000004</v>
+        <v>18.149999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11787,35 +11933,35 @@
         <v>19</v>
       </c>
       <c r="C16" s="21">
-        <f t="shared" ref="C16:J16" si="9">C15/40</f>
+        <f t="shared" ref="C16:J16" si="10">C15/40</f>
         <v>20.824999999999999</v>
       </c>
       <c r="D16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.95</v>
       </c>
       <c r="E16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.65</v>
       </c>
       <c r="F16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17.175000000000001</v>
       </c>
       <c r="G16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17.2</v>
       </c>
       <c r="H16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.2249999999999996</v>
       </c>
       <c r="I16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23.274999999999999</v>
       </c>
       <c r="J16" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>104.3</v>
       </c>
       <c r="K16" s="23"/>
@@ -11824,36 +11970,36 @@
         <v>19</v>
       </c>
       <c r="O16" s="21">
-        <f t="shared" ref="O16:V16" si="10">O15/40</f>
-        <v>0</v>
+        <f t="shared" ref="O16:V16" si="11">O15/40</f>
+        <v>9.65</v>
       </c>
       <c r="P16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.55</v>
       </c>
       <c r="Q16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.05</v>
       </c>
       <c r="R16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>21.8</v>
       </c>
       <c r="S16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>14</v>
       </c>
       <c r="T16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.7</v>
       </c>
       <c r="U16" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>20.375</v>
       </c>
       <c r="V16" s="22">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>82.125</v>
       </c>
       <c r="W16" s="23"/>
       <c r="Y16" s="42">
@@ -11862,11 +12008,11 @@
       </c>
       <c r="Z16" s="43">
         <f>Z15/40</f>
-        <v>0</v>
+        <v>0.62875000000000003</v>
       </c>
       <c r="AA16" s="44">
         <f>AA15/40</f>
-        <v>1.0825</v>
+        <v>0.45374999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -11933,103 +12079,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12046,16 +12192,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12063,16 +12209,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12152,18 +12298,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>172</v>
+      </c>
+      <c r="D8" s="11">
+        <v>92</v>
+      </c>
+      <c r="E8" s="11">
+        <v>72</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>95</v>
+      </c>
+      <c r="H8" s="11">
+        <v>50</v>
+      </c>
+      <c r="I8" s="11">
+        <v>99</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>14.5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>11</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -12183,7 +12345,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -12191,7 +12353,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -12199,18 +12361,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>42</v>
+      </c>
+      <c r="D9" s="11">
+        <v>40</v>
+      </c>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>40</v>
+      </c>
+      <c r="G9" s="11">
+        <v>70</v>
+      </c>
+      <c r="H9" s="11">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
+        <v>80</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="K9" s="12">
+        <v>9</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -12230,7 +12408,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -12238,7 +12416,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9.0500000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -12246,18 +12424,28 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11">
+        <v>200</v>
+      </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11">
+        <v>15</v>
+      </c>
+      <c r="H10" s="11">
+        <v>15</v>
+      </c>
+      <c r="I10" s="11">
+        <v>10</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -12277,7 +12465,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -12285,30 +12473,46 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="C11" s="11">
+        <v>120</v>
+      </c>
+      <c r="D11" s="11">
+        <v>147</v>
+      </c>
+      <c r="E11" s="11">
+        <v>132</v>
+      </c>
+      <c r="F11" s="11">
+        <v>77</v>
+      </c>
+      <c r="G11" s="11">
+        <v>101</v>
+      </c>
+      <c r="H11" s="11">
+        <v>30</v>
+      </c>
+      <c r="I11" s="11">
+        <v>41</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>16.2</v>
+      </c>
+      <c r="K11" s="12">
+        <v>7</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -12324,7 +12528,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -12332,30 +12536,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>43</v>
+      </c>
+      <c r="C12" s="11">
+        <v>187</v>
+      </c>
+      <c r="D12" s="11">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11">
+        <v>106</v>
+      </c>
+      <c r="F12" s="11">
+        <v>15</v>
+      </c>
+      <c r="G12" s="11">
+        <v>51</v>
+      </c>
+      <c r="H12" s="11">
+        <v>46</v>
+      </c>
+      <c r="I12" s="11">
+        <v>40</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>11.375</v>
+      </c>
+      <c r="K12" s="12">
+        <v>11</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -12371,7 +12591,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.375</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -12379,12 +12599,14 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.375</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -12395,7 +12617,9 @@
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -12423,35 +12647,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>2285</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -12491,7 +12715,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>57.125</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -12499,7 +12723,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>57.125</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12509,35 +12733,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>18.024999999999999</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>57.125</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -12579,7 +12803,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>1.4281250000000001</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -12587,7 +12811,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>1.4281250000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12654,103 +12878,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12767,16 +12991,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12784,16 +13008,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13375,103 +13599,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13488,16 +13712,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13505,16 +13729,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14096,103 +14320,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14209,16 +14433,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14226,16 +14450,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14817,103 +15041,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14930,16 +15154,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14947,16 +15171,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15538,103 +15762,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15651,16 +15875,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15668,16 +15892,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16259,103 +16483,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16372,16 +16596,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16389,16 +16613,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16980,103 +17204,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17093,16 +17317,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17110,16 +17334,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17701,103 +17925,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17814,16 +18038,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17831,16 +18055,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18424,103 +18648,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18537,16 +18761,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18554,16 +18778,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19207,103 +19431,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19320,16 +19544,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19337,16 +19561,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19892,16 +20116,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="80" t="s">
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -20272,103 +20496,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20385,16 +20609,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20402,16 +20626,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21089,111 +21313,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="K2" s="47"/>
       <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="47"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21210,16 +21434,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81" t="s">
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -21228,16 +21452,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21973,103 +22197,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22086,16 +22310,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22103,16 +22327,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22859,103 +23083,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22972,16 +23196,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22989,16 +23213,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -23725,103 +23949,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -23838,16 +24062,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23855,16 +24079,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -24540,103 +24764,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="Y3" s="80" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="Y3" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -24653,16 +24877,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -24670,16 +24894,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E8B55-6C12-4428-8451-5BA6BC975965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451810DE-4C12-42C8-958A-264F91D2292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="19" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="20" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -673,6 +673,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,103 +1059,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="76" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1171,16 +1172,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1188,16 +1189,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -1868,103 +1869,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -1981,16 +1982,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1998,16 +1999,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -2727,103 +2728,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -2840,16 +2841,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2857,16 +2858,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -3625,103 +3626,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -3738,16 +3739,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3755,16 +3756,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -4549,103 +4550,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -4662,16 +4663,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4679,16 +4680,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -5461,103 +5462,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -5574,16 +5575,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5591,16 +5592,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -6182,103 +6183,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -6295,16 +6296,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6312,16 +6313,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7061,103 +7062,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7174,16 +7175,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7191,16 +7192,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -7782,103 +7783,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -7895,16 +7896,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7912,16 +7913,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -8702,103 +8703,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -8815,16 +8816,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8832,16 +8833,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -9547,103 +9548,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -9660,16 +9661,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9677,16 +9678,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -10409,10 +10410,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="80" t="s">
+      <c r="L1" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="80"/>
+      <c r="M1" s="81"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -10424,103 +10425,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -10537,16 +10538,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10554,16 +10555,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11098,7 +11099,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE02268-B5C0-4F7D-B124-8932172B8A1F}">
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -11146,103 +11147,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -11259,16 +11260,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11276,16 +11277,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -11499,7 +11500,7 @@
         <v>16</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V14" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>7.8</v>
       </c>
       <c r="W9" s="12">
@@ -11682,29 +11683,39 @@
       <c r="N12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="11"/>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="S12" s="11">
+        <v>1</v>
+      </c>
+      <c r="T12" s="11">
+        <v>1</v>
+      </c>
+      <c r="U12" s="11">
+        <v>1</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>1.075</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>6.8</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.075</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>6.8</v>
+        <v>5.7249999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -11744,29 +11755,45 @@
       <c r="N13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="11">
+        <v>69</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>22</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11">
+        <v>23</v>
+      </c>
+      <c r="T13" s="11">
+        <v>10</v>
+      </c>
+      <c r="U13" s="11">
+        <v>20</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="18"/>
+        <v>3.6</v>
+      </c>
+      <c r="W13" s="18">
+        <v>5</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>2.8250000000000002</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>2.8250000000000002</v>
+        <v>-0.77499999999999991</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -11826,7 +11853,7 @@
         <v>680</v>
       </c>
       <c r="V14" s="15">
-        <f t="shared" si="1"/>
+        <f>SUM(O14:U14)/40</f>
         <v>56.975000000000001</v>
       </c>
       <c r="W14" s="18"/>
@@ -11883,7 +11910,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="75">
         <f>SUM(O8:O14)</f>
-        <v>386</v>
+        <v>495</v>
       </c>
       <c r="P15" s="75">
         <f t="shared" ref="P15:U15" si="9">SUM(P8:P14)</f>
@@ -11891,7 +11918,7 @@
       </c>
       <c r="Q15" s="75">
         <f t="shared" si="9"/>
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="R15" s="75">
         <f t="shared" si="9"/>
@@ -11899,19 +11926,19 @@
       </c>
       <c r="S15" s="75">
         <f t="shared" si="9"/>
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="T15" s="75">
         <f t="shared" si="9"/>
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="U15" s="75">
         <f t="shared" si="9"/>
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="V15" s="28">
         <f>SUM(O15:U15)</f>
-        <v>3285</v>
+        <v>3472</v>
       </c>
       <c r="W15" s="31"/>
       <c r="Y15" s="36">
@@ -11920,11 +11947,11 @@
       </c>
       <c r="Z15" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>25.150000000000002</v>
+        <v>29.825000000000003</v>
       </c>
       <c r="AA15" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>18.149999999999999</v>
+        <v>13.475</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11971,7 +11998,7 @@
       </c>
       <c r="O16" s="21">
         <f t="shared" ref="O16:V16" si="11">O15/40</f>
-        <v>9.65</v>
+        <v>12.375</v>
       </c>
       <c r="P16" s="21">
         <f t="shared" si="11"/>
@@ -11979,7 +12006,7 @@
       </c>
       <c r="Q16" s="21">
         <f t="shared" si="11"/>
-        <v>5.05</v>
+        <v>5.6</v>
       </c>
       <c r="R16" s="21">
         <f t="shared" si="11"/>
@@ -11987,19 +12014,19 @@
       </c>
       <c r="S16" s="21">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="T16" s="21">
         <f t="shared" si="11"/>
-        <v>5.7</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="U16" s="21">
         <f t="shared" si="11"/>
-        <v>20.375</v>
+        <v>20.9</v>
       </c>
       <c r="V16" s="22">
         <f t="shared" si="11"/>
-        <v>82.125</v>
+        <v>86.8</v>
       </c>
       <c r="W16" s="23"/>
       <c r="Y16" s="42">
@@ -12008,11 +12035,66 @@
       </c>
       <c r="Z16" s="43">
         <f>Z15/40</f>
-        <v>0.62875000000000003</v>
+        <v>0.74562500000000009</v>
       </c>
       <c r="AA16" s="44">
         <f>AA15/40</f>
-        <v>0.45374999999999999</v>
+        <v>0.33687499999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X20">
+        <v>20467</v>
+      </c>
+      <c r="Y20">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="21" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X21">
+        <v>20557</v>
+      </c>
+      <c r="Y21">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="22" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X22">
+        <v>18860</v>
+      </c>
+      <c r="Y22">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="23" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X23" s="76">
+        <f>SUM(X20:X22)</f>
+        <v>59884</v>
+      </c>
+      <c r="Y23">
+        <v>6272</v>
+      </c>
+    </row>
+    <row r="24" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="Y24">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="25" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="Y25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="Y26">
+        <f>SUM(Y20:Y25)</f>
+        <v>20181</v>
+      </c>
+    </row>
+    <row r="27" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="W27">
+        <f>X23-Y26</f>
+        <v>39703</v>
       </c>
     </row>
   </sheetData>
@@ -12046,7 +12128,7 @@
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
@@ -12079,103 +12161,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12192,16 +12274,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12209,16 +12291,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -12588,7 +12670,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="12">
+        <v>7</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>11.375</v>
@@ -12878,103 +12962,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -12991,16 +13075,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13008,16 +13092,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -13599,103 +13683,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -13712,16 +13796,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13729,16 +13813,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -14320,103 +14404,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -14433,16 +14517,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14450,16 +14534,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15041,103 +15125,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15154,16 +15238,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15171,16 +15255,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -15762,103 +15846,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -15875,16 +15959,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15892,16 +15976,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -16483,103 +16567,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -16596,16 +16680,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16613,16 +16697,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17204,103 +17288,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -17317,16 +17401,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17334,16 +17418,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -17925,103 +18009,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18038,16 +18122,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18055,16 +18139,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -18648,103 +18732,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -18761,16 +18845,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18778,16 +18862,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -19431,103 +19515,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -19544,16 +19628,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19561,16 +19645,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -20116,16 +20200,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="Y3" s="81" t="s">
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="2:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.35">
       <c r="Y5" s="32" t="s">
@@ -20496,103 +20580,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -20609,16 +20693,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20626,16 +20710,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -21313,111 +21397,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="K2" s="47"/>
       <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="47"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="K3" s="47"/>
       <c r="L3" s="47"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="47"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -21434,16 +21518,16 @@
       <c r="C6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82" t="s">
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
       <c r="J6" s="50"/>
       <c r="K6" s="51"/>
       <c r="L6" s="47"/>
@@ -21452,16 +21536,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -22197,103 +22281,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -22310,16 +22394,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22327,16 +22411,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -23083,103 +23167,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -23196,16 +23280,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23213,16 +23297,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -23949,103 +24033,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -24062,16 +24146,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -24079,16 +24163,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>
@@ -24764,103 +24848,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="32" t="s">
         <v>0</v>
       </c>
@@ -24877,16 +24961,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -24894,16 +24978,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="33"/>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451810DE-4C12-42C8-958A-264F91D2292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39B41E2-A5A6-48CA-8F00-BB1884467506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="20" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="44">
   <si>
     <t>Booking</t>
   </si>
@@ -12413,29 +12413,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>160</v>
+      </c>
+      <c r="P8" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>60</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>95</v>
+      </c>
+      <c r="T8" s="11">
+        <v>50</v>
+      </c>
+      <c r="U8" s="11">
+        <v>75</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>14.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -12476,29 +12492,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>40</v>
+      </c>
+      <c r="P9" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>50</v>
+      </c>
+      <c r="U9" s="11">
+        <v>80</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W9" s="12">
+        <v>9</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>9.0500000000000007</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>9.0500000000000007</v>
+        <v>5.0000000000000711E-2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -12533,29 +12565,39 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="11">
+        <v>200</v>
+      </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="S10" s="11">
+        <v>15</v>
+      </c>
+      <c r="T10" s="11">
+        <v>15</v>
+      </c>
+      <c r="U10" s="11">
+        <v>10</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -12596,29 +12638,45 @@
       <c r="N11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>120</v>
+      </c>
+      <c r="P11" s="11">
+        <v>132</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>122</v>
+      </c>
+      <c r="R11" s="11">
+        <v>62</v>
+      </c>
+      <c r="S11" s="11">
+        <v>101</v>
+      </c>
+      <c r="T11" s="11">
+        <v>30</v>
+      </c>
+      <c r="U11" s="11">
+        <v>41</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>15.2</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>16.2</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>16.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -12659,19 +12717,33 @@
       <c r="N12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>107</v>
+      </c>
+      <c r="P12" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>106</v>
+      </c>
+      <c r="R12" s="11">
+        <v>15</v>
+      </c>
+      <c r="S12" s="11">
+        <v>51</v>
+      </c>
+      <c r="T12" s="11">
+        <v>40</v>
+      </c>
+      <c r="U12" s="11">
+        <v>40</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="W12" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
@@ -12679,11 +12751,11 @@
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>11.375</v>
+        <v>2.1500000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -12766,35 +12838,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>2097</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -12803,11 +12875,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>52.425000000000004</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>57.125</v>
+        <v>4.7000000000000011</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12854,35 +12926,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>15.675000000000001</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>52.424999999999997</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -12891,11 +12963,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>1.3106250000000002</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.4281250000000001</v>
+        <v>0.11750000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -12921,8 +12993,7 @@
     <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
@@ -13181,18 +13252,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>10</v>
+      </c>
+      <c r="G8" s="11">
+        <v>95</v>
+      </c>
+      <c r="H8" s="11">
+        <v>55</v>
+      </c>
+      <c r="I8" s="11">
+        <v>105</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>9.875</v>
+      </c>
+      <c r="K8" s="12">
+        <v>12</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -13212,7 +13299,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>9.875</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -13220,7 +13307,7 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>9.875</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -13228,18 +13315,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>78</v>
+      </c>
+      <c r="E9" s="11">
+        <v>67</v>
+      </c>
+      <c r="F9" s="11">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11">
+        <v>100</v>
+      </c>
+      <c r="H9" s="11">
+        <v>80</v>
+      </c>
+      <c r="I9" s="11">
+        <v>80</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>12.5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>12</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -13259,7 +13362,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -13267,7 +13370,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -13275,18 +13378,34 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>212</v>
+      </c>
+      <c r="D10" s="11">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11">
+        <v>17</v>
+      </c>
+      <c r="F10" s="11">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
+        <v>6</v>
+      </c>
+      <c r="H10" s="11">
+        <v>6</v>
+      </c>
+      <c r="I10" s="11">
+        <v>6</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="K10" s="12">
+        <v>11</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -13306,7 +13425,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.7249999999999996</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -13314,30 +13433,46 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.7249999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C11" s="11">
+        <v>30</v>
+      </c>
+      <c r="D11" s="11">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>24</v>
+      </c>
+      <c r="F11" s="11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11">
+        <v>45</v>
+      </c>
+      <c r="H11" s="11">
+        <v>28</v>
+      </c>
+      <c r="I11" s="11">
+        <v>39</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>4.75</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -13353,7 +13488,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -13361,30 +13496,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>32</v>
+      </c>
+      <c r="D12" s="11">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11">
+        <v>12</v>
+      </c>
+      <c r="G12" s="11">
+        <v>26</v>
+      </c>
+      <c r="H12" s="11">
+        <v>6</v>
+      </c>
+      <c r="I12" s="11">
+        <v>12</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>3.15</v>
+      </c>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -13400,7 +13551,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -13408,23 +13559,44 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="D13" s="11">
+        <v>1450</v>
+      </c>
+      <c r="E13" s="11">
+        <v>210</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1005</v>
+      </c>
+      <c r="G13" s="11">
+        <v>995</v>
+      </c>
+      <c r="H13" s="11">
+        <v>1450</v>
+      </c>
+      <c r="I13" s="11">
+        <v>560</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>141.75</v>
+      </c>
+      <c r="K13" s="18">
+        <v>12</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -13436,7 +13608,7 @@
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>141.75</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -13444,7 +13616,7 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>141.75</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -13452,35 +13624,35 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1267</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1625</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>7150</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
@@ -13520,7 +13692,7 @@
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>178.75</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -13528,7 +13700,7 @@
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>178.75</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13538,35 +13710,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>39.975000000000001</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26.475000000000001</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31.675000000000001</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>40.625</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>178.75</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -13608,7 +13780,7 @@
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>4.46875</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
@@ -13616,7 +13788,7 @@
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>4.46875</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39B41E2-A5A6-48CA-8F00-BB1884467506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E3347B-6F94-46C0-9ADF-758ABC3AFBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -13285,29 +13285,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>10</v>
+      </c>
+      <c r="S8" s="11">
+        <v>95</v>
+      </c>
+      <c r="T8" s="11">
+        <v>55</v>
+      </c>
+      <c r="U8" s="11">
+        <v>105</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>7.875</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>9.875</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>7.875</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>9.875</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -13348,29 +13364,45 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>60</v>
+      </c>
+      <c r="P9" s="11">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>35</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>80</v>
+      </c>
+      <c r="T9" s="11">
+        <v>60</v>
+      </c>
+      <c r="U9" s="11">
+        <v>60</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>8.5</v>
+      </c>
+      <c r="W9" s="12">
+        <v>10</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>12.5</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>12.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -13411,29 +13443,45 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>152</v>
+      </c>
+      <c r="P10" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>11</v>
+      </c>
+      <c r="R10" s="11">
+        <v>5</v>
+      </c>
+      <c r="S10" s="11">
+        <v>6</v>
+      </c>
+      <c r="T10" s="11">
+        <v>6</v>
+      </c>
+      <c r="U10" s="11">
+        <v>6</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4.9249999999999998</v>
+      </c>
+      <c r="W10" s="12">
+        <v>8</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>6.7249999999999996</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9249999999999998</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>6.7249999999999996</v>
+        <v>1.7999999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -13474,29 +13522,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>18</v>
+      </c>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>24</v>
+      </c>
+      <c r="R11" s="11">
+        <v>12</v>
+      </c>
+      <c r="S11" s="11">
+        <v>39</v>
+      </c>
+      <c r="T11" s="11">
+        <v>28</v>
+      </c>
+      <c r="U11" s="11">
+        <v>39</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4.3</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>4.75</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>4.75</v>
+        <v>0.45000000000000018</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -13537,29 +13601,45 @@
       <c r="N12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>26</v>
+      </c>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>20</v>
+      </c>
+      <c r="R12" s="11">
+        <v>12</v>
+      </c>
+      <c r="S12" s="11">
+        <v>20</v>
+      </c>
+      <c r="T12" s="11">
+        <v>6</v>
+      </c>
+      <c r="U12" s="11">
+        <v>12</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>2.7</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>3.15</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>3.15</v>
+        <v>0.44999999999999973</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -13659,35 +13739,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>1132</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -13696,11 +13776,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>178.75</v>
+        <v>150.44999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13747,35 +13827,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -13784,11 +13864,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.70750000000000002</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>4.46875</v>
+        <v>3.7612499999999995</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E3347B-6F94-46C0-9ADF-758ABC3AFBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89D11FB-918D-44DD-BAC0-7D084E83F82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="26" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="51">
   <si>
     <t>Booking</t>
   </si>
@@ -187,6 +187,27 @@
   </si>
   <si>
     <t xml:space="preserve">Furqan </t>
+  </si>
+  <si>
+    <t>Zeshan</t>
+  </si>
+  <si>
+    <t>Salman Butt</t>
+  </si>
+  <si>
+    <t>Umair Rehman</t>
+  </si>
+  <si>
+    <t>Shakoor (LMT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqeel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qasim </t>
   </si>
 </sst>
 </file>
@@ -14154,13 +14175,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -14171,14 +14192,14 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="74">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
@@ -14201,13 +14222,13 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -14218,14 +14239,14 @@
       <c r="N9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="74">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
@@ -14248,13 +14269,13 @@
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -14265,14 +14286,14 @@
       <c r="N10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14295,13 +14316,13 @@
       <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -14312,14 +14333,14 @@
       <c r="N11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14342,13 +14363,13 @@
       <c r="B12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -14359,14 +14380,14 @@
       <c r="N12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14387,25 +14408,25 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="74"/>
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
@@ -14612,15 +14633,14 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -14873,7 +14893,7 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -14890,37 +14910,53 @@
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="O8" s="11">
+        <v>80</v>
+      </c>
+      <c r="P8" s="11">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>115</v>
+      </c>
+      <c r="T8" s="11">
+        <v>80</v>
+      </c>
+      <c r="U8" s="11">
+        <v>190</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>12.6</v>
+      </c>
+      <c r="W8" s="12">
+        <v>14</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -14937,37 +14973,53 @@
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="O9" s="11">
+        <v>160</v>
+      </c>
+      <c r="P9" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>58</v>
+      </c>
+      <c r="U9" s="11">
+        <v>110</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
+        <v>12.95</v>
+      </c>
+      <c r="W9" s="12">
+        <v>14</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>12.95</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -14984,37 +15036,53 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="O10" s="11">
+        <v>80</v>
+      </c>
+      <c r="P10" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>40</v>
+      </c>
+      <c r="S10" s="11">
+        <v>100</v>
+      </c>
+      <c r="T10" s="11">
+        <v>100</v>
+      </c>
+      <c r="U10" s="11">
+        <v>60</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-9.8000000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -15031,37 +15099,53 @@
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="O11" s="11">
+        <v>64</v>
+      </c>
+      <c r="P11" s="11">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>32</v>
+      </c>
+      <c r="R11" s="11">
+        <v>47</v>
+      </c>
+      <c r="S11" s="11">
+        <v>36</v>
+      </c>
+      <c r="T11" s="11">
+        <v>37</v>
+      </c>
+      <c r="U11" s="11">
+        <v>65</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.95</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -15078,36 +15162,54 @@
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="11">
+        <v>70</v>
+      </c>
+      <c r="P12" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="11">
         <v>20</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>20</v>
+      </c>
+      <c r="T12" s="11">
+        <v>10</v>
+      </c>
+      <c r="U12" s="11">
+        <v>10</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.5</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -15118,27 +15220,48 @@
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="N13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="11">
+        <v>40</v>
+      </c>
+      <c r="P13" s="11">
+        <v>199</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>200</v>
+      </c>
+      <c r="R13" s="11">
+        <v>320</v>
+      </c>
+      <c r="S13" s="11">
+        <v>280</v>
+      </c>
+      <c r="T13" s="11">
+        <v>280</v>
+      </c>
+      <c r="U13" s="11">
+        <v>300</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>40.475000000000001</v>
+      </c>
+      <c r="W13" s="12">
+        <v>5</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40.475000000000001</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-40.475000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -15181,35 +15304,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>3491</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -15218,11 +15341,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>87.275000000000006</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>-87.275000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15269,35 +15392,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>12.35</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.4250000000000007</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.175000000000001</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.525</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.125</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18.375</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>87.275000000000006</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -15306,11 +15429,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>2.1818750000000002</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>-2.1818750000000002</v>
       </c>
     </row>
   </sheetData>
@@ -15341,7 +15464,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -15596,42 +15719,74 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>160</v>
+      </c>
+      <c r="D8" s="11">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>40</v>
+      </c>
+      <c r="H8" s="11">
+        <v>40</v>
+      </c>
+      <c r="I8" s="11">
+        <v>80</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>160</v>
+      </c>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>40</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>9</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
@@ -15641,24 +15796,40 @@
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="C9" s="11">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11">
+        <v>42</v>
+      </c>
+      <c r="E9" s="11">
+        <v>42</v>
+      </c>
+      <c r="F9" s="11">
+        <v>40</v>
+      </c>
+      <c r="G9" s="11">
+        <v>131</v>
+      </c>
+      <c r="H9" s="11">
+        <v>99</v>
+      </c>
+      <c r="I9" s="11">
+        <v>160</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>13.15</v>
+      </c>
+      <c r="K9" s="12">
+        <v>15</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -15674,7 +15845,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>13.15</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -15682,77 +15853,125 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="C10" s="11">
+        <v>104</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>40</v>
+      </c>
+      <c r="G10" s="11">
+        <v>73</v>
+      </c>
+      <c r="H10" s="11">
+        <v>18</v>
+      </c>
+      <c r="I10" s="11">
+        <v>25</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="K10" s="12">
+        <v>9</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="O10" s="11">
+        <v>92</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>40</v>
+      </c>
+      <c r="S10" s="11">
+        <v>73</v>
+      </c>
+      <c r="T10" s="11">
+        <v>18</v>
+      </c>
+      <c r="U10" s="11">
+        <v>25</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>6.2</v>
+      </c>
+      <c r="W10" s="12">
+        <v>8</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.29999999999999982</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C11" s="11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="11">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>22</v>
+      </c>
+      <c r="H11" s="11">
+        <v>10</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>1.4750000000000001</v>
+      </c>
+      <c r="K11" s="12">
+        <v>4</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -15768,7 +15987,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -15776,59 +15995,93 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4750000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>53</v>
+      </c>
+      <c r="D12" s="11">
+        <v>22</v>
+      </c>
+      <c r="E12" s="11">
+        <v>21</v>
+      </c>
+      <c r="F12" s="11">
+        <v>19</v>
+      </c>
+      <c r="G12" s="11">
+        <v>15</v>
+      </c>
+      <c r="H12" s="11">
+        <v>15</v>
+      </c>
+      <c r="I12" s="11">
+        <v>15</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="O12" s="11">
+        <v>3</v>
+      </c>
+      <c r="P12" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>12</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>22</v>
+      </c>
+      <c r="T12" s="11">
+        <v>10</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>1.325</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.6749999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -15839,7 +16092,9 @@
       <c r="J13" s="15"/>
       <c r="K13" s="18"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -15867,83 +16122,83 @@
       <c r="B14" s="7"/>
       <c r="C14" s="25">
         <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="J14" s="28">
         <f>SUM(C14:I14)</f>
-        <v>0</v>
+        <v>1365</v>
       </c>
       <c r="K14" s="31"/>
       <c r="M14" s="1"/>
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
+        <v>34.125</v>
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>16.524999999999999</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
+        <v>17.599999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15953,35 +16208,35 @@
       </c>
       <c r="C15" s="21">
         <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="D15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.0250000000000004</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I15" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>34.125</v>
       </c>
       <c r="K15" s="23"/>
       <c r="M15" s="1"/>
@@ -15990,48 +16245,48 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.375</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.625</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.524999999999999</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
         <f>Y14/40</f>
-        <v>0</v>
+        <v>0.85312500000000002</v>
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0</v>
+        <v>0.41312499999999996</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0</v>
+        <v>0.43999999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -16771,11 +17026,11 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5F6109-5400-4343-A102-C2C414DDFBDF}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -16783,7 +17038,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -17036,24 +17291,40 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>130</v>
+      </c>
+      <c r="F8" s="11">
+        <v>120</v>
+      </c>
+      <c r="G8" s="11">
+        <v>83</v>
+      </c>
+      <c r="H8" s="11">
+        <v>80</v>
+      </c>
+      <c r="I8" s="11">
+        <v>80</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>14.824999999999999</v>
+      </c>
+      <c r="K8" s="12">
+        <v>10</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -17069,7 +17340,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -17077,30 +17348,46 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>14.824999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="C9" s="11">
+        <v>60</v>
+      </c>
+      <c r="D9" s="11">
+        <v>15</v>
+      </c>
+      <c r="E9" s="11">
+        <v>45</v>
+      </c>
+      <c r="F9" s="11">
+        <v>80</v>
+      </c>
+      <c r="G9" s="11">
+        <v>55</v>
+      </c>
+      <c r="H9" s="11">
+        <v>55</v>
+      </c>
+      <c r="I9" s="11">
+        <v>98</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K9" s="12">
+        <v>5</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -17115,39 +17402,55 @@
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
-        <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y16" si="2">J9</f>
+        <v>10.199999999999999</v>
       </c>
       <c r="Z9" s="40">
-        <f t="shared" ref="Z9:Z13" si="3">V9</f>
+        <f t="shared" ref="Z9:Z16" si="3">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="41">
-        <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <f t="shared" ref="AA9:AA16" si="4">Y9-Z9</f>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="11">
+        <v>172</v>
+      </c>
+      <c r="D10" s="11">
+        <v>12</v>
+      </c>
+      <c r="E10" s="11">
+        <v>12</v>
+      </c>
+      <c r="F10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11">
+        <v>66</v>
+      </c>
+      <c r="H10" s="11">
+        <v>63</v>
+      </c>
+      <c r="I10" s="11">
+        <v>33</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>9.35</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -17163,7 +17466,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -17171,30 +17474,46 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C11" s="11">
+        <v>70</v>
+      </c>
+      <c r="D11" s="11">
+        <v>19</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="11">
+        <v>25</v>
+      </c>
+      <c r="G11" s="11">
+        <v>21</v>
+      </c>
+      <c r="H11" s="11">
+        <v>10</v>
+      </c>
+      <c r="I11" s="11">
+        <v>21</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K11" s="12">
+        <v>6</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -17210,7 +17529,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -17218,30 +17537,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>132</v>
+      </c>
+      <c r="D12" s="11">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11">
+        <v>54</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>18</v>
+      </c>
+      <c r="H12" s="11">
+        <v>24</v>
+      </c>
+      <c r="I12" s="11">
+        <v>12</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.3</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -17257,7 +17592,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -17265,12 +17600,14 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>48</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -17278,8 +17615,13 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="J13" s="15">
+        <v>9</v>
+      </c>
+      <c r="K13" s="12">
+        <v>8</v>
+      </c>
+      <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
       <c r="O13" s="11"/>
@@ -17290,190 +17632,289 @@
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
-      <c r="Y13" s="39">
+      <c r="W13" s="12"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="41"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="15">
+        <v>12</v>
+      </c>
+      <c r="K14" s="12">
+        <v>10</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="12"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="41"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="15">
+        <v>13</v>
+      </c>
+      <c r="K15" s="12">
+        <v>20</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="12"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="41"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="18"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="18"/>
+      <c r="Y16" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="40">
+      <c r="Z16" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="41">
+      <c r="AA16" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25">
-        <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="25">
+        <f t="shared" ref="C17:I17" si="5">SUM(C8:C16)</f>
+        <v>514</v>
+      </c>
+      <c r="D17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25">
+        <v>78</v>
+      </c>
+      <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="25">
+        <v>251</v>
+      </c>
+      <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
+        <v>241</v>
+      </c>
+      <c r="G17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
+        <v>243</v>
+      </c>
+      <c r="H17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
+        <v>232</v>
+      </c>
+      <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <f>SUM(C14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="25">
-        <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="25">
+        <v>244</v>
+      </c>
+      <c r="J17" s="28">
+        <f>SUM(C17:I17)</f>
+        <v>1803</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="25">
+        <f t="shared" ref="O17:U17" si="6">SUM(O8:O16)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U14" s="25">
+      <c r="U17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V14" s="28">
-        <f>SUM(O14:U14)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="31"/>
-      <c r="Y14" s="36">
-        <f>SUM(Y8:Y13)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="37">
-        <f>SUM(Z8:Z13)</f>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="38">
-        <f>SUM(AA8:AA13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+      <c r="V17" s="28">
+        <f>SUM(O17:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="Y17" s="36">
+        <f>SUM(Y8:Y16)</f>
+        <v>45.074999999999996</v>
+      </c>
+      <c r="Z17" s="37">
+        <f>SUM(Z8:Z16)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="38">
+        <f>SUM(AA8:AA16)</f>
+        <v>45.074999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="21">
-        <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="C18" s="21">
+        <f t="shared" ref="C18:J18" si="7">C17/40</f>
+        <v>12.85</v>
+      </c>
+      <c r="D18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
+        <v>1.95</v>
+      </c>
+      <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
+        <v>6.2750000000000004</v>
+      </c>
+      <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
+        <v>6.0250000000000004</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
+        <v>6.0750000000000002</v>
+      </c>
+      <c r="H18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
+        <v>5.8</v>
+      </c>
+      <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
+        <v>6.1</v>
+      </c>
+      <c r="J18" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="23"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="20" t="s">
+        <v>45.075000000000003</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="O15" s="21">
-        <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
+      <c r="O18" s="21">
+        <f t="shared" ref="O18:V18" si="8">O17/40</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S15" s="21">
+      <c r="S18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T15" s="21">
+      <c r="T18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U15" s="21">
+      <c r="U18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V15" s="22">
+      <c r="V18" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W15" s="23"/>
-      <c r="Y15" s="42">
-        <f>Y14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="43">
-        <f>Z14/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44">
-        <f>AA14/40</f>
-        <v>0</v>
+      <c r="W18" s="23"/>
+      <c r="Y18" s="42">
+        <f>Y17/40</f>
+        <v>1.1268749999999998</v>
+      </c>
+      <c r="Z18" s="43">
+        <f>Z17/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="44">
+        <f>AA17/40</f>
+        <v>1.1268749999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89D11FB-918D-44DD-BAC0-7D084E83F82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75EE2A9-2C98-451C-99B9-1FE6C19883F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="26" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <sheet name="31" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="51">
   <si>
     <t>Booking</t>
   </si>
@@ -15831,29 +15832,45 @@
       <c r="N9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>12</v>
+      </c>
+      <c r="P9" s="11">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>42</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <v>131</v>
+      </c>
+      <c r="T9" s="11">
+        <v>99</v>
+      </c>
+      <c r="U9" s="11">
+        <v>160</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>13.15</v>
+      </c>
+      <c r="W9" s="12">
+        <v>15</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
         <v>13.15</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
-        <v>0</v>
+        <v>13.15</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>13.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15973,29 +15990,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>53</v>
+      </c>
+      <c r="P11" s="11">
+        <v>22</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>21</v>
+      </c>
+      <c r="R11" s="11">
+        <v>19</v>
+      </c>
+      <c r="S11" s="11">
+        <v>15</v>
+      </c>
+      <c r="T11" s="11">
+        <v>15</v>
+      </c>
+      <c r="U11" s="11">
+        <v>15</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W11" s="12">
+        <v>7</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>1.4750000000000001</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>1.4750000000000001</v>
+        <v>-2.5249999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -16095,11 +16128,17 @@
       <c r="N13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="11">
+        <v>41</v>
+      </c>
       <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="Q13" s="11">
+        <v>1</v>
+      </c>
       <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
+      <c r="S13" s="11">
+        <v>1</v>
+      </c>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="15"/>
@@ -16157,35 +16196,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>255</v>
+        <v>361</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>661</v>
+        <v>1390</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -16194,11 +16233,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>16.524999999999999</v>
+        <v>33.674999999999997</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>17.599999999999998</v>
+        <v>0.44999999999999973</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16245,35 +16284,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>6.375</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>1.1499999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>3.375</v>
+        <v>7.05</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>1.7</v>
+        <v>4.55</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>2.625</v>
+        <v>7</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>16.524999999999999</v>
+        <v>34.75</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -16282,11 +16321,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0.41312499999999996</v>
+        <v>0.84187499999999993</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>0.43999999999999995</v>
+        <v>1.1249999999999993E-2</v>
       </c>
     </row>
   </sheetData>
@@ -17294,29 +17333,29 @@
         <v>44</v>
       </c>
       <c r="C8" s="11">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="D8" s="11">
         <v>20</v>
       </c>
       <c r="E8" s="11">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F8" s="11">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H8" s="11">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="I8" s="11">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>14.824999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="K8" s="12">
         <v>10</v>
@@ -17326,29 +17365,45 @@
       <c r="N8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>100</v>
+      </c>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>40</v>
+      </c>
+      <c r="S8" s="11">
+        <v>55</v>
+      </c>
+      <c r="T8" s="11">
+        <v>10</v>
+      </c>
+      <c r="U8" s="11">
+        <v>15</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>14.824999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>14.824999999999999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17389,29 +17444,45 @@
       <c r="N9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>40</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>40</v>
+      </c>
+      <c r="S9" s="11">
+        <v>15</v>
+      </c>
+      <c r="T9" s="11">
+        <v>15</v>
+      </c>
+      <c r="U9" s="11">
+        <v>58</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>5.2</v>
+      </c>
+      <c r="W9" s="12">
+        <v>3</v>
+      </c>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y16" si="2">J9</f>
         <v>10.199999999999999</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z16" si="3">V9</f>
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA16" si="4">Y9-Z9</f>
-        <v>10.199999999999999</v>
+        <v>4.9999999999999991</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -17452,29 +17523,45 @@
       <c r="N10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>160</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>65</v>
+      </c>
+      <c r="T10" s="11">
+        <v>63</v>
+      </c>
+      <c r="U10" s="11">
+        <v>33</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.0250000000000004</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>9.35</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.0250000000000004</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>9.35</v>
+        <v>1.3249999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -17515,29 +17602,45 @@
       <c r="N11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>58</v>
+      </c>
+      <c r="P11" s="11">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>25</v>
+      </c>
+      <c r="S11" s="11">
+        <v>21</v>
+      </c>
+      <c r="T11" s="11">
+        <v>10</v>
+      </c>
+      <c r="U11" s="11">
+        <v>21</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>4.4000000000000004</v>
+        <v>0.30000000000000071</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -17578,29 +17681,45 @@
       <c r="N12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>140</v>
+      </c>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>48</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>27</v>
+      </c>
+      <c r="T12" s="11">
+        <v>27</v>
+      </c>
+      <c r="U12" s="11">
+        <v>22</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6.9</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>6.3</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>6.3</v>
+        <v>-0.60000000000000053</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -17623,7 +17742,9 @@
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -17750,7 +17871,7 @@
       <c r="B17" s="7"/>
       <c r="C17" s="25">
         <f t="shared" ref="C17:I17" si="5">SUM(C8:C16)</f>
-        <v>514</v>
+        <v>654</v>
       </c>
       <c r="D17" s="25">
         <f t="shared" si="5"/>
@@ -17758,75 +17879,75 @@
       </c>
       <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="G17" s="25">
         <f t="shared" si="5"/>
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="H17" s="25">
         <f t="shared" si="5"/>
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="J17" s="28">
         <f>SUM(C17:I17)</f>
-        <v>1803</v>
+        <v>1590</v>
       </c>
       <c r="K17" s="31"/>
       <c r="M17" s="1"/>
       <c r="N17" s="7"/>
       <c r="O17" s="25">
         <f t="shared" ref="O17:U17" si="6">SUM(O8:O16)</f>
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="P17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="S17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="T17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="U17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="V17" s="28">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="W17" s="31"/>
       <c r="Y17" s="36">
         <f>SUM(Y8:Y16)</f>
-        <v>45.074999999999996</v>
+        <v>39.749999999999993</v>
       </c>
       <c r="Z17" s="37">
         <f>SUM(Z8:Z16)</f>
-        <v>0</v>
+        <v>30.725000000000001</v>
       </c>
       <c r="AA17" s="38">
         <f>SUM(AA8:AA16)</f>
-        <v>45.074999999999996</v>
+        <v>9.0249999999999986</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17836,7 +17957,7 @@
       </c>
       <c r="C18" s="21">
         <f t="shared" ref="C18:J18" si="7">C17/40</f>
-        <v>12.85</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="7"/>
@@ -17844,27 +17965,27 @@
       </c>
       <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>6.2750000000000004</v>
+        <v>3.5249999999999999</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>6.0250000000000004</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="G18" s="21">
         <f t="shared" si="7"/>
-        <v>6.0750000000000002</v>
+        <v>5.375</v>
       </c>
       <c r="H18" s="21">
         <f t="shared" si="7"/>
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>6.1</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="J18" s="22">
         <f t="shared" si="7"/>
-        <v>45.075000000000003</v>
+        <v>39.75</v>
       </c>
       <c r="K18" s="23"/>
       <c r="M18" s="1"/>
@@ -17873,48 +17994,48 @@
       </c>
       <c r="O18" s="21">
         <f t="shared" ref="O18:V18" si="8">O17/40</f>
-        <v>0</v>
+        <v>12.45</v>
       </c>
       <c r="P18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.2749999999999999</v>
       </c>
       <c r="Q18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.625</v>
       </c>
       <c r="S18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5750000000000002</v>
       </c>
       <c r="T18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="U18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.7250000000000001</v>
       </c>
       <c r="V18" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30.725000000000001</v>
       </c>
       <c r="W18" s="23"/>
       <c r="Y18" s="42">
         <f>Y17/40</f>
-        <v>1.1268749999999998</v>
+        <v>0.9937499999999998</v>
       </c>
       <c r="Z18" s="43">
         <f>Z17/40</f>
-        <v>0</v>
+        <v>0.76812500000000006</v>
       </c>
       <c r="AA18" s="44">
         <f>AA17/40</f>
-        <v>1.1268749999999998</v>
+        <v>0.22562499999999996</v>
       </c>
     </row>
   </sheetData>
@@ -17933,11 +18054,11 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8009CC4-0AF4-4E7F-B044-5E07B86C5D3C}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -17945,7 +18066,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -18198,24 +18319,40 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60</v>
+      </c>
+      <c r="E8" s="11">
+        <v>50</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>193</v>
+      </c>
+      <c r="H8" s="11">
+        <v>78</v>
+      </c>
+      <c r="I8" s="11">
+        <v>253</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>17.850000000000001</v>
+      </c>
+      <c r="K8" s="12">
+        <v>20</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -18231,7 +18368,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -18239,30 +18376,40 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>17.850000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>80</v>
+      </c>
+      <c r="G9" s="11">
+        <v>40</v>
+      </c>
+      <c r="H9" s="11">
+        <v>40</v>
+      </c>
       <c r="I9" s="11"/>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>3</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -18278,7 +18425,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -18286,30 +18433,46 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="C10" s="11">
+        <v>252</v>
+      </c>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>112</v>
+      </c>
+      <c r="H10" s="11">
+        <v>100</v>
+      </c>
+      <c r="I10" s="11">
+        <v>60</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>13.6</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -18325,7 +18488,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -18333,30 +18496,46 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C11" s="11">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11">
+        <v>27</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="11">
+        <v>27</v>
+      </c>
+      <c r="G11" s="11">
+        <v>12</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>12</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="K11" s="12">
+        <v>2</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -18372,7 +18551,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -18380,30 +18559,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>104</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
         <v>20</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="F12" s="11">
+        <v>12</v>
+      </c>
+      <c r="G12" s="11">
+        <v>10</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>18</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K12" s="12">
+        <v>8</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -18419,7 +18614,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -18427,23 +18622,44 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="D13" s="11">
+        <v>120</v>
+      </c>
+      <c r="E13" s="11">
+        <v>160</v>
+      </c>
+      <c r="F13" s="11">
+        <v>760</v>
+      </c>
+      <c r="G13" s="11">
+        <v>260</v>
+      </c>
+      <c r="H13" s="11">
+        <v>100</v>
+      </c>
+      <c r="I13" s="11">
+        <v>320</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="K13" s="18">
+        <v>2</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -18455,7 +18671,7 @@
       <c r="W13" s="18"/>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
@@ -18463,179 +18679,278 @@
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25">
-        <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="15">
+        <v>13</v>
+      </c>
+      <c r="K14" s="18">
+        <v>10</v>
+      </c>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="18"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="41"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="15">
+        <v>17</v>
+      </c>
+      <c r="K15" s="18">
+        <v>13</v>
+      </c>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="18"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="41"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="15">
+        <v>7</v>
+      </c>
+      <c r="K16" s="18">
+        <v>8</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="18"/>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="41"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="25">
+        <f t="shared" ref="C17:I17" si="5">SUM(C8:C13)</f>
+        <v>448</v>
+      </c>
+      <c r="D17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25">
+        <v>217</v>
+      </c>
+      <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="25">
+        <v>290</v>
+      </c>
+      <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
+        <v>879</v>
+      </c>
+      <c r="G17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
+        <v>627</v>
+      </c>
+      <c r="H17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
+        <v>318</v>
+      </c>
+      <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <f>SUM(C14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="25">
-        <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="25">
+        <v>663</v>
+      </c>
+      <c r="J17" s="28">
+        <f>SUM(C17:I17)</f>
+        <v>3442</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="25">
+        <f t="shared" ref="O17:U17" si="6">SUM(O8:O13)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U14" s="25">
+      <c r="U17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V14" s="28">
-        <f>SUM(O14:U14)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="31"/>
-      <c r="Y14" s="36">
+      <c r="V17" s="28">
+        <f>SUM(O17:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="Y17" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="37">
+        <v>86.050000000000011</v>
+      </c>
+      <c r="Z17" s="37">
         <f>SUM(Z8:Z13)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="38">
+      <c r="AA17" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+        <v>86.050000000000011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="21">
-        <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="C18" s="21">
+        <f t="shared" ref="C18:J18" si="7">C17/40</f>
+        <v>11.2</v>
+      </c>
+      <c r="D18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
+        <v>5.4249999999999998</v>
+      </c>
+      <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
+        <v>7.25</v>
+      </c>
+      <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
+        <v>21.975000000000001</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
+        <v>15.675000000000001</v>
+      </c>
+      <c r="H18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
+        <v>7.95</v>
+      </c>
+      <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="23"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="20" t="s">
+        <v>16.574999999999999</v>
+      </c>
+      <c r="J18" s="22">
+        <f>SUM(J8:J16)</f>
+        <v>123.05000000000001</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="O15" s="21">
-        <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
+      <c r="O18" s="21">
+        <f t="shared" ref="O18:V18" si="8">O17/40</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S15" s="21">
+      <c r="S18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T15" s="21">
+      <c r="T18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U15" s="21">
+      <c r="U18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V15" s="22">
+      <c r="V18" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W15" s="23"/>
-      <c r="Y15" s="42">
-        <f>Y14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="43">
-        <f>Z14/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44">
-        <f>AA14/40</f>
-        <v>0</v>
+      <c r="W18" s="23"/>
+      <c r="Y18" s="42">
+        <f>Y17/40</f>
+        <v>2.1512500000000001</v>
+      </c>
+      <c r="Z18" s="43">
+        <f>Z17/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="44">
+        <f>AA17/40</f>
+        <v>2.1512500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75EE2A9-2C98-451C-99B9-1FE6C19883F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CB54E-9CB8-4C8B-842E-7E2C339A4ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="28" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,6 @@
     <sheet name="31" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="52">
   <si>
     <t>Booking</t>
   </si>
@@ -209,6 +208,9 @@
   </si>
   <si>
     <t xml:space="preserve">Qasim </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -15854,7 +15856,7 @@
         <v>160</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>13.15</v>
       </c>
       <c r="W9" s="12">
@@ -16129,31 +16131,45 @@
         <v>47</v>
       </c>
       <c r="O13" s="11">
-        <v>41</v>
-      </c>
-      <c r="P13" s="11"/>
+        <f>41+160</f>
+        <v>201</v>
+      </c>
+      <c r="P13" s="11">
+        <v>200</v>
+      </c>
       <c r="Q13" s="11">
-        <v>1</v>
-      </c>
-      <c r="R13" s="11"/>
+        <v>121</v>
+      </c>
+      <c r="R13" s="11">
+        <v>440</v>
+      </c>
       <c r="S13" s="11">
-        <v>1</v>
-      </c>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+        <v>181</v>
+      </c>
+      <c r="T13" s="11">
+        <v>140</v>
+      </c>
+      <c r="U13" s="11">
+        <v>560</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>46.075000000000003</v>
+      </c>
+      <c r="W13" s="18">
+        <v>6</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46.075000000000003</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-46.075000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -16196,35 +16212,35 @@
       <c r="N14" s="7"/>
       <c r="O14" s="25">
         <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>361</v>
+        <v>521</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="Q14" s="25">
         <f t="shared" si="6"/>
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="R14" s="25">
         <f t="shared" si="6"/>
-        <v>99</v>
+        <v>539</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>282</v>
+        <v>462</v>
       </c>
       <c r="T14" s="25">
         <f t="shared" si="6"/>
-        <v>182</v>
+        <v>322</v>
       </c>
       <c r="U14" s="25">
         <f t="shared" si="6"/>
-        <v>280</v>
+        <v>840</v>
       </c>
       <c r="V14" s="28">
         <f>SUM(O14:U14)</f>
-        <v>1390</v>
+        <v>3190</v>
       </c>
       <c r="W14" s="31"/>
       <c r="Y14" s="36">
@@ -16233,11 +16249,11 @@
       </c>
       <c r="Z14" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>33.674999999999997</v>
+        <v>79.75</v>
       </c>
       <c r="AA14" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>0.44999999999999973</v>
+        <v>-45.625</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16284,35 +16300,35 @@
       </c>
       <c r="O15" s="21">
         <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>9.0250000000000004</v>
+        <v>13.025</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="8"/>
-        <v>2.75</v>
+        <v>7.75</v>
       </c>
       <c r="Q15" s="21">
         <f t="shared" si="8"/>
-        <v>1.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="8"/>
-        <v>2.4750000000000001</v>
+        <v>13.475</v>
       </c>
       <c r="S15" s="21">
         <f t="shared" si="8"/>
-        <v>7.05</v>
+        <v>11.55</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="8"/>
-        <v>4.55</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="U15" s="21">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="V15" s="22">
         <f t="shared" si="8"/>
-        <v>34.75</v>
+        <v>79.75</v>
       </c>
       <c r="W15" s="23"/>
       <c r="Y15" s="42">
@@ -16321,11 +16337,11 @@
       </c>
       <c r="Z15" s="43">
         <f>Z14/40</f>
-        <v>0.84187499999999993</v>
+        <v>1.9937499999999999</v>
       </c>
       <c r="AA15" s="44">
         <f>AA14/40</f>
-        <v>1.1249999999999993E-2</v>
+        <v>-1.140625</v>
       </c>
     </row>
   </sheetData>
@@ -17080,11 +17096,10 @@
     <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -17466,7 +17481,7 @@
         <v>58</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>5.2</v>
       </c>
       <c r="W9" s="12">
@@ -17745,17 +17760,39 @@
       <c r="N13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="12"/>
+      <c r="O13" s="11">
+        <v>280</v>
+      </c>
+      <c r="P13" s="11">
+        <v>720</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1080</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1279</v>
+      </c>
+      <c r="S13" s="11">
+        <v>1200</v>
+      </c>
+      <c r="T13" s="11">
+        <v>1357</v>
+      </c>
+      <c r="U13" s="11">
+        <v>2680</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>214.9</v>
+      </c>
+      <c r="W13" s="12">
+        <v>7</v>
+      </c>
       <c r="Y13" s="39"/>
-      <c r="Z13" s="40"/>
+      <c r="Z13" s="40">
+        <f t="shared" si="3"/>
+        <v>214.9</v>
+      </c>
       <c r="AA13" s="41"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -17906,35 +17943,35 @@
       <c r="N17" s="7"/>
       <c r="O17" s="25">
         <f t="shared" ref="O17:U17" si="6">SUM(O8:O16)</f>
-        <v>498</v>
+        <v>778</v>
       </c>
       <c r="P17" s="25">
         <f t="shared" si="6"/>
-        <v>51</v>
+        <v>771</v>
       </c>
       <c r="Q17" s="25">
         <f t="shared" si="6"/>
-        <v>118</v>
+        <v>1198</v>
       </c>
       <c r="R17" s="25">
         <f t="shared" si="6"/>
-        <v>105</v>
+        <v>1384</v>
       </c>
       <c r="S17" s="25">
         <f t="shared" si="6"/>
-        <v>183</v>
+        <v>1383</v>
       </c>
       <c r="T17" s="25">
         <f t="shared" si="6"/>
-        <v>125</v>
+        <v>1482</v>
       </c>
       <c r="U17" s="25">
         <f t="shared" si="6"/>
-        <v>149</v>
+        <v>2829</v>
       </c>
       <c r="V17" s="28">
         <f>SUM(O17:U17)</f>
-        <v>1229</v>
+        <v>9825</v>
       </c>
       <c r="W17" s="31"/>
       <c r="Y17" s="36">
@@ -17943,7 +17980,7 @@
       </c>
       <c r="Z17" s="37">
         <f>SUM(Z8:Z16)</f>
-        <v>30.725000000000001</v>
+        <v>245.625</v>
       </c>
       <c r="AA17" s="38">
         <f>SUM(AA8:AA16)</f>
@@ -17994,35 +18031,35 @@
       </c>
       <c r="O18" s="21">
         <f t="shared" ref="O18:V18" si="8">O17/40</f>
-        <v>12.45</v>
+        <v>19.45</v>
       </c>
       <c r="P18" s="21">
         <f t="shared" si="8"/>
-        <v>1.2749999999999999</v>
+        <v>19.274999999999999</v>
       </c>
       <c r="Q18" s="21">
         <f t="shared" si="8"/>
-        <v>2.95</v>
+        <v>29.95</v>
       </c>
       <c r="R18" s="21">
         <f t="shared" si="8"/>
-        <v>2.625</v>
+        <v>34.6</v>
       </c>
       <c r="S18" s="21">
         <f t="shared" si="8"/>
-        <v>4.5750000000000002</v>
+        <v>34.575000000000003</v>
       </c>
       <c r="T18" s="21">
         <f t="shared" si="8"/>
-        <v>3.125</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="U18" s="21">
         <f t="shared" si="8"/>
-        <v>3.7250000000000001</v>
+        <v>70.724999999999994</v>
       </c>
       <c r="V18" s="22">
         <f t="shared" si="8"/>
-        <v>30.725000000000001</v>
+        <v>245.625</v>
       </c>
       <c r="W18" s="23"/>
       <c r="Y18" s="42">
@@ -18031,7 +18068,7 @@
       </c>
       <c r="Z18" s="43">
         <f>Z17/40</f>
-        <v>0.76812500000000006</v>
+        <v>6.140625</v>
       </c>
       <c r="AA18" s="44">
         <f>AA17/40</f>
@@ -18384,13 +18421,17 @@
       <c r="B9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="C9" s="11">
+        <v>16</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
       <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
         <v>40</v>
-      </c>
-      <c r="F9" s="11">
-        <v>80</v>
       </c>
       <c r="G9" s="11">
         <v>40</v>
@@ -18398,13 +18439,15 @@
       <c r="H9" s="11">
         <v>40</v>
       </c>
-      <c r="I9" s="11"/>
+      <c r="I9" s="11">
+        <v>40</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K9" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -18425,7 +18468,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
         <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z9" s="40">
         <f t="shared" ref="Z9:Z13" si="3">V9</f>
@@ -18433,7 +18476,7 @@
       </c>
       <c r="AA9" s="41">
         <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -18786,7 +18829,7 @@
       <c r="B17" s="7"/>
       <c r="C17" s="25">
         <f t="shared" ref="C17:I17" si="5">SUM(C8:C13)</f>
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="D17" s="25">
         <f t="shared" si="5"/>
@@ -18794,11 +18837,11 @@
       </c>
       <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="G17" s="25">
         <f t="shared" si="5"/>
@@ -18810,11 +18853,11 @@
       </c>
       <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>663</v>
+        <v>703</v>
       </c>
       <c r="J17" s="28">
         <f>SUM(C17:I17)</f>
-        <v>3442</v>
+        <v>3418</v>
       </c>
       <c r="K17" s="31"/>
       <c r="M17" s="1"/>
@@ -18854,7 +18897,7 @@
       <c r="W17" s="31"/>
       <c r="Y17" s="36">
         <f>SUM(Y8:Y13)</f>
-        <v>86.050000000000011</v>
+        <v>85.45</v>
       </c>
       <c r="Z17" s="37">
         <f>SUM(Z8:Z13)</f>
@@ -18862,7 +18905,7 @@
       </c>
       <c r="AA17" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>86.050000000000011</v>
+        <v>85.45</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -18871,8 +18914,8 @@
         <v>19</v>
       </c>
       <c r="C18" s="21">
-        <f t="shared" ref="C18:J18" si="7">C17/40</f>
-        <v>11.2</v>
+        <f t="shared" ref="C18:I18" si="7">C17/40</f>
+        <v>11.6</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="7"/>
@@ -18880,11 +18923,11 @@
       </c>
       <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>21.975000000000001</v>
+        <v>20.975000000000001</v>
       </c>
       <c r="G18" s="21">
         <f t="shared" si="7"/>
@@ -18896,11 +18939,11 @@
       </c>
       <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>16.574999999999999</v>
+        <v>17.574999999999999</v>
       </c>
       <c r="J18" s="22">
         <f>SUM(J8:J16)</f>
-        <v>123.05000000000001</v>
+        <v>122.45</v>
       </c>
       <c r="K18" s="23"/>
       <c r="M18" s="1"/>
@@ -18942,7 +18985,7 @@
       <c r="W18" s="23"/>
       <c r="Y18" s="42">
         <f>Y17/40</f>
-        <v>2.1512500000000001</v>
+        <v>2.13625</v>
       </c>
       <c r="Z18" s="43">
         <f>Z17/40</f>
@@ -18950,7 +18993,7 @@
       </c>
       <c r="AA18" s="44">
         <f>AA17/40</f>
-        <v>2.1512500000000001</v>
+        <v>2.13625</v>
       </c>
     </row>
   </sheetData>
@@ -18969,11 +19012,11 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753F267E-9AB4-4A14-B158-934CAE66BC78}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -18981,7 +19024,7 @@
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -19234,24 +19277,40 @@
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60</v>
+      </c>
+      <c r="E8" s="11">
+        <v>60</v>
+      </c>
+      <c r="F8" s="11">
+        <v>80</v>
+      </c>
+      <c r="G8" s="11">
+        <v>55</v>
+      </c>
+      <c r="H8" s="11">
+        <v>130</v>
+      </c>
+      <c r="I8" s="11">
+        <v>135</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="K8" s="12">
+        <v>18</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -19267,7 +19326,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="39">
         <f>J8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
@@ -19275,30 +19334,46 @@
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="11">
+        <v>40</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>100</v>
+      </c>
+      <c r="H9" s="11">
+        <v>124</v>
+      </c>
+      <c r="I9" s="11">
+        <v>256</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="15">
-        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="12">
+        <v>17</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -19308,27 +19383,27 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="39">
-        <f t="shared" ref="Y9:Y13" si="2">J9</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y16" si="2">J9</f>
+        <v>14</v>
       </c>
       <c r="Z9" s="40">
-        <f t="shared" ref="Z9:Z13" si="3">V9</f>
+        <f t="shared" ref="Z9:Z16" si="3">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="41">
-        <f t="shared" ref="AA9:AA13" si="4">Y9-Z9</f>
-        <v>0</v>
+        <f t="shared" ref="AA9:AA16" si="4">Y9-Z9</f>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -19345,7 +19420,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -19375,24 +19450,40 @@
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="C11" s="11">
+        <v>80</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>36</v>
+      </c>
+      <c r="H11" s="11">
+        <v>52</v>
+      </c>
+      <c r="I11" s="11">
+        <v>34</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>5.05</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -19408,7 +19499,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
@@ -19416,30 +19507,46 @@
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C12" s="11">
+        <v>164</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>92</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>40</v>
+      </c>
+      <c r="H12" s="11">
+        <v>120</v>
+      </c>
+      <c r="I12" s="11">
+        <v>80</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>12.4</v>
+      </c>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -19455,7 +19562,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
@@ -19463,12 +19570,14 @@
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -19476,10 +19585,16 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="18"/>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -19487,191 +19602,312 @@
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
-      <c r="Y13" s="39">
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="12"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="41"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="15">
+        <v>20</v>
+      </c>
+      <c r="K14" s="12">
+        <v>18</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="12"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="41"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="15">
+        <v>30</v>
+      </c>
+      <c r="K15" s="12">
+        <v>15</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="12"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="41"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="15">
+        <v>6</v>
+      </c>
+      <c r="K16" s="18">
+        <v>8</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="18"/>
+      <c r="Y16" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="40">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="41">
+      <c r="AA16" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="25">
-        <f t="shared" ref="C14:I14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="25">
+        <f t="shared" ref="C17:I17" si="5">SUM(C8:C16)</f>
+        <v>364</v>
+      </c>
+      <c r="D17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25">
+        <v>60</v>
+      </c>
+      <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="25">
+        <v>192</v>
+      </c>
+      <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
+        <v>80</v>
+      </c>
+      <c r="G17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
+        <v>231</v>
+      </c>
+      <c r="H17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
+        <v>426</v>
+      </c>
+      <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <f>SUM(C14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="25">
-        <f t="shared" ref="O14:U14" si="6">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="25">
+        <v>505</v>
+      </c>
+      <c r="J17" s="28">
+        <f>SUM(C17:I17)</f>
+        <v>1858</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="25">
+        <f t="shared" ref="O17:U17" si="6">SUM(O8:O16)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U14" s="25">
+      <c r="U17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V14" s="28">
-        <f>SUM(O14:U14)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="31"/>
-      <c r="Y14" s="36">
-        <f>SUM(Y8:Y13)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="37">
-        <f>SUM(Z8:Z13)</f>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="38">
-        <f>SUM(AA8:AA13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+      <c r="V17" s="28">
+        <f>SUM(O17:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="Y17" s="36">
+        <f>SUM(Y8:Y16)</f>
+        <v>52.449999999999996</v>
+      </c>
+      <c r="Z17" s="37">
+        <f>SUM(Z8:Z16)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="38">
+        <f>SUM(AA8:AA16)</f>
+        <v>52.449999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="21">
-        <f t="shared" ref="C15:J15" si="7">C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="C18" s="21">
+        <f t="shared" ref="C18:J18" si="7">C17/40</f>
+        <v>9.1</v>
+      </c>
+      <c r="D18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
+        <v>4.8</v>
+      </c>
+      <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
+        <v>2</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
+        <v>5.7750000000000004</v>
+      </c>
+      <c r="H18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
+        <v>10.65</v>
+      </c>
+      <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
+        <v>12.625</v>
+      </c>
+      <c r="J18" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="23"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="20" t="s">
+        <v>46.45</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="M18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="O15" s="21">
-        <f t="shared" ref="O15:V15" si="8">O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
+      <c r="O18" s="21">
+        <f t="shared" ref="O18:V18" si="8">O17/40</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S15" s="21">
+      <c r="S18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T15" s="21">
+      <c r="T18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U15" s="21">
+      <c r="U18" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V15" s="22">
+      <c r="V18" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W15" s="23"/>
-      <c r="Y15" s="42">
-        <f>Y14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="43">
-        <f>Z14/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="44">
-        <f>AA14/40</f>
-        <v>0</v>
+      <c r="W18" s="23"/>
+      <c r="Y18" s="42">
+        <f>Y17/40</f>
+        <v>1.3112499999999998</v>
+      </c>
+      <c r="Z18" s="43">
+        <f>Z17/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="44">
+        <f>AA17/40</f>
+        <v>1.3112499999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CB54E-9CB8-4C8B-842E-7E2C339A4ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F31071D-C465-493F-9CC1-EEF6AFB643BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="28" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -18391,29 +18391,45 @@
       <c r="N8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>80</v>
+      </c>
+      <c r="P8" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>153</v>
+      </c>
+      <c r="T8" s="11">
+        <v>38</v>
+      </c>
+      <c r="U8" s="11">
+        <v>213</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>14.85</v>
+      </c>
+      <c r="W8" s="12">
+        <v>19</v>
+      </c>
       <c r="Y8" s="39">
         <f>J8</f>
         <v>17.850000000000001</v>
       </c>
       <c r="Z8" s="40">
         <f>V8</f>
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="AA8" s="41">
         <f>Y8-Z8</f>
-        <v>17.850000000000001</v>
+        <v>3.0000000000000018</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -18462,7 +18478,7 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
@@ -18517,29 +18533,45 @@
       <c r="N10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>239</v>
+      </c>
+      <c r="P10" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>10</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>111</v>
+      </c>
+      <c r="T10" s="11">
+        <v>78</v>
+      </c>
+      <c r="U10" s="11">
+        <v>40</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>12.2</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
         <v>13.6</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>13.6</v>
+        <v>1.4000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -18581,28 +18613,36 @@
         <v>24</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="P11" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>15</v>
+      </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="W11" s="12">
+        <v>1</v>
+      </c>
       <c r="Y11" s="39">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
       <c r="Z11" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="41">
         <f t="shared" si="4"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -18643,29 +18683,45 @@
       <c r="N12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>60</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>10</v>
+      </c>
+      <c r="R12" s="11">
+        <v>12</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>18</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="39">
         <f t="shared" si="2"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="Z12" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" s="41">
         <f t="shared" si="4"/>
-        <v>4.0999999999999996</v>
+        <v>1.5999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -18704,25 +18760,42 @@
         <v>17</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="18"/>
+      <c r="P13" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>160</v>
+      </c>
+      <c r="R13" s="11">
+        <v>600</v>
+      </c>
+      <c r="S13" s="11">
+        <v>240</v>
+      </c>
+      <c r="T13" s="11">
+        <v>100</v>
+      </c>
+      <c r="U13" s="11">
+        <v>320</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>38.5</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2</v>
+      </c>
       <c r="Y13" s="39">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="Z13" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="AA13" s="41">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
@@ -18864,35 +18937,35 @@
       <c r="N17" s="7"/>
       <c r="O17" s="25">
         <f t="shared" ref="O17:U17" si="6">SUM(O8:O13)</f>
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="P17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="Q17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="R17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="S17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="T17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="U17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="V17" s="28">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
+        <v>2762</v>
       </c>
       <c r="W17" s="31"/>
       <c r="Y17" s="36">
@@ -18901,11 +18974,11 @@
       </c>
       <c r="Z17" s="37">
         <f>SUM(Z8:Z13)</f>
-        <v>0</v>
+        <v>69.05</v>
       </c>
       <c r="AA17" s="38">
         <f>SUM(AA8:AA13)</f>
-        <v>85.45</v>
+        <v>16.400000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -18952,35 +19025,35 @@
       </c>
       <c r="O18" s="21">
         <f t="shared" ref="O18:V18" si="8">O17/40</f>
-        <v>0</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="P18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.125</v>
       </c>
       <c r="Q18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.675000000000001</v>
       </c>
       <c r="S18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="T18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="U18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.775</v>
       </c>
       <c r="V18" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>69.05</v>
       </c>
       <c r="W18" s="23"/>
       <c r="Y18" s="42">
@@ -18989,11 +19062,11 @@
       </c>
       <c r="Z18" s="43">
         <f>Z17/40</f>
-        <v>0</v>
+        <v>1.7262499999999998</v>
       </c>
       <c r="AA18" s="44">
         <f>AA17/40</f>
-        <v>2.13625</v>
+        <v>0.41000000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -19364,7 +19437,7 @@
         <v>256</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>14</v>
       </c>
       <c r="K9" s="12">
@@ -19405,18 +19478,34 @@
       <c r="B10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>104</v>
+      </c>
+      <c r="D10" s="11">
+        <v>6</v>
+      </c>
+      <c r="E10" s="11">
+        <v>6</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>60</v>
+      </c>
+      <c r="H10" s="11">
+        <v>80</v>
+      </c>
+      <c r="I10" s="11">
+        <v>80</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>8.4</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -19436,7 +19525,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z10" s="40">
         <f t="shared" si="3"/>
@@ -19444,7 +19533,7 @@
       </c>
       <c r="AA10" s="41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -19578,18 +19667,34 @@
       <c r="B13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="11">
+        <v>80</v>
+      </c>
+      <c r="D13" s="11">
+        <v>200</v>
+      </c>
+      <c r="E13" s="11">
+        <v>200</v>
+      </c>
+      <c r="F13" s="11">
+        <v>200</v>
+      </c>
+      <c r="G13" s="11">
+        <v>120</v>
+      </c>
+      <c r="H13" s="11">
+        <v>120</v>
+      </c>
+      <c r="I13" s="11">
+        <v>120</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>26</v>
+      </c>
+      <c r="K13" s="12">
+        <v>1</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -19741,35 +19846,35 @@
       <c r="B17" s="7"/>
       <c r="C17" s="25">
         <f t="shared" ref="C17:I17" si="5">SUM(C8:C16)</f>
-        <v>364</v>
+        <v>548</v>
       </c>
       <c r="D17" s="25">
         <f t="shared" si="5"/>
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="E17" s="25">
         <f t="shared" si="5"/>
-        <v>192</v>
+        <v>398</v>
       </c>
       <c r="F17" s="25">
         <f t="shared" si="5"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="G17" s="25">
         <f t="shared" si="5"/>
-        <v>231</v>
+        <v>411</v>
       </c>
       <c r="H17" s="25">
         <f t="shared" si="5"/>
-        <v>426</v>
+        <v>626</v>
       </c>
       <c r="I17" s="25">
         <f t="shared" si="5"/>
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="J17" s="28">
         <f>SUM(C17:I17)</f>
-        <v>1858</v>
+        <v>3234</v>
       </c>
       <c r="K17" s="31"/>
       <c r="M17" s="1"/>
@@ -19809,7 +19914,7 @@
       <c r="W17" s="31"/>
       <c r="Y17" s="36">
         <f>SUM(Y8:Y16)</f>
-        <v>52.449999999999996</v>
+        <v>60.849999999999994</v>
       </c>
       <c r="Z17" s="37">
         <f>SUM(Z8:Z16)</f>
@@ -19817,7 +19922,7 @@
       </c>
       <c r="AA17" s="38">
         <f>SUM(AA8:AA16)</f>
-        <v>52.449999999999996</v>
+        <v>60.849999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19826,36 +19931,36 @@
         <v>19</v>
       </c>
       <c r="C18" s="21">
-        <f t="shared" ref="C18:J18" si="7">C17/40</f>
-        <v>9.1</v>
+        <f t="shared" ref="C18:I18" si="7">C17/40</f>
+        <v>13.7</v>
       </c>
       <c r="D18" s="21">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>6.65</v>
       </c>
       <c r="E18" s="21">
         <f t="shared" si="7"/>
-        <v>4.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="21">
         <f t="shared" si="7"/>
-        <v>5.7750000000000004</v>
+        <v>10.275</v>
       </c>
       <c r="H18" s="21">
         <f t="shared" si="7"/>
-        <v>10.65</v>
+        <v>15.65</v>
       </c>
       <c r="I18" s="21">
         <f t="shared" si="7"/>
-        <v>12.625</v>
+        <v>17.625</v>
       </c>
       <c r="J18" s="22">
-        <f t="shared" si="7"/>
-        <v>46.45</v>
+        <f>SUM(J8:J16)</f>
+        <v>136.85</v>
       </c>
       <c r="K18" s="23"/>
       <c r="M18" s="1" t="s">
@@ -19899,7 +20004,7 @@
       <c r="W18" s="23"/>
       <c r="Y18" s="42">
         <f>Y17/40</f>
-        <v>1.3112499999999998</v>
+        <v>1.5212499999999998</v>
       </c>
       <c r="Z18" s="43">
         <f>Z17/40</f>
@@ -19907,7 +20012,7 @@
       </c>
       <c r="AA18" s="44">
         <f>AA17/40</f>
-        <v>1.3112499999999998</v>
+        <v>1.5212499999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Aug_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E830D25-593C-479B-9C9D-DD5E2C83A7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D871B8-C357-4BEA-A589-736010428751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" firstSheet="2" activeTab="29" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" firstSheet="2" activeTab="30" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -22248,29 +22248,45 @@
       <c r="N7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="O7" s="11">
+        <v>693</v>
+      </c>
+      <c r="P7" s="11">
+        <v>70</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>70</v>
+      </c>
+      <c r="R7" s="11">
+        <v>80</v>
+      </c>
+      <c r="S7" s="11">
+        <v>103</v>
+      </c>
+      <c r="T7" s="11">
+        <v>98</v>
+      </c>
+      <c r="U7" s="11">
+        <v>193</v>
+      </c>
       <c r="V7" s="15">
         <f>SUM(O7:U7)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="12"/>
+        <v>32.674999999999997</v>
+      </c>
+      <c r="W7" s="12">
+        <v>16</v>
+      </c>
       <c r="Y7" s="36">
         <f>J7</f>
         <v>34.924999999999997</v>
       </c>
       <c r="Z7" s="37">
         <f>V7</f>
-        <v>0</v>
+        <v>32.674999999999997</v>
       </c>
       <c r="AA7" s="38">
         <f>Y7-Z7</f>
-        <v>34.924999999999997</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
@@ -22311,29 +22327,45 @@
       <c r="N8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>40</v>
+      </c>
+      <c r="P8" s="11">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>50</v>
+      </c>
+      <c r="R8" s="11">
+        <v>70</v>
+      </c>
+      <c r="S8" s="11">
+        <v>59</v>
+      </c>
+      <c r="T8" s="11">
+        <v>35</v>
+      </c>
+      <c r="U8" s="11">
+        <v>45</v>
+      </c>
       <c r="V8" s="15">
-        <f t="shared" ref="V8:V11" si="1">SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <f t="shared" ref="V8:V12" si="1">SUM(O8:U8)/40</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W8" s="12">
+        <v>18</v>
+      </c>
       <c r="Y8" s="36">
         <f t="shared" ref="Y8:Y16" si="2">J8</f>
         <v>11.5</v>
       </c>
       <c r="Z8" s="37">
         <f t="shared" ref="Z8:Z16" si="3">V8</f>
-        <v>0</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AA8" s="38">
         <f t="shared" ref="AA8:AA16" si="4">Y8-Z8</f>
-        <v>11.5</v>
+        <v>2.3000000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22374,29 +22406,45 @@
       <c r="N9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>318</v>
+      </c>
+      <c r="P9" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>6</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>90</v>
+      </c>
+      <c r="T9" s="11">
+        <v>72</v>
+      </c>
+      <c r="U9" s="11">
+        <v>72</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>14.1</v>
+      </c>
+      <c r="W9" s="12">
+        <v>13</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" si="2"/>
         <v>14.1</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" si="4"/>
-        <v>14.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22437,29 +22485,45 @@
       <c r="N10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>56</v>
+      </c>
+      <c r="P10" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>12</v>
+      </c>
+      <c r="R10" s="11">
+        <v>12</v>
+      </c>
+      <c r="S10" s="11">
+        <v>76</v>
+      </c>
+      <c r="T10" s="11">
+        <v>72</v>
+      </c>
+      <c r="U10" s="11">
+        <v>102</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>1.4499999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -22500,29 +22564,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>145</v>
+      </c>
+      <c r="P11" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>38</v>
+      </c>
+      <c r="R11" s="11">
+        <v>10</v>
+      </c>
+      <c r="S11" s="11">
+        <v>53</v>
+      </c>
+      <c r="T11" s="11">
+        <v>10</v>
+      </c>
+      <c r="U11" s="11">
+        <v>40</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.7750000000000004</v>
+      </c>
+      <c r="W11" s="12">
+        <v>10</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>9.7750000000000004</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.7750000000000004</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>9.7750000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22550,13 +22630,26 @@
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+      <c r="Q12" s="11">
+        <v>119</v>
+      </c>
+      <c r="R12" s="11">
+        <v>200</v>
+      </c>
       <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="12"/>
+      <c r="T12" s="11">
+        <v>79</v>
+      </c>
+      <c r="U12" s="11">
+        <v>318</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="1"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="36"/>
       <c r="Z12" s="37"/>
       <c r="AA12" s="38"/>
@@ -22744,35 +22837,35 @@
       <c r="N17" s="7"/>
       <c r="O17" s="25">
         <f t="shared" ref="O17:U17" si="6">SUM(O7:O16)</f>
-        <v>0</v>
+        <v>1252</v>
       </c>
       <c r="P17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="Q17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="R17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="S17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="T17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="U17" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="V17" s="26">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
+        <v>3608</v>
       </c>
       <c r="W17" s="28"/>
       <c r="Y17" s="33">
@@ -22781,11 +22874,11 @@
       </c>
       <c r="Z17" s="34">
         <f>SUM(Z7:Z16)</f>
-        <v>0</v>
+        <v>72.300000000000011</v>
       </c>
       <c r="AA17" s="35">
         <f>SUM(AA7:AA16)</f>
-        <v>80.300000000000011</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22835,35 +22928,35 @@
       </c>
       <c r="O18" s="21">
         <f t="shared" ref="O18:V18" si="8">O17/40</f>
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="P18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.375</v>
       </c>
       <c r="R18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="S18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.5250000000000004</v>
       </c>
       <c r="T18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="U18" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="V18" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="W18" s="23"/>
       <c r="Y18" s="39">
@@ -22872,11 +22965,11 @@
       </c>
       <c r="Z18" s="40">
         <f>Z17/40</f>
-        <v>0</v>
+        <v>1.8075000000000003</v>
       </c>
       <c r="AA18" s="41">
         <f>AA17/40</f>
-        <v>2.0075000000000003</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
